--- a/output/预警客户以及临界客户信息表.xlsx
+++ b/output/预警客户以及临界客户信息表.xlsx
@@ -21,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,177 +433,177 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>旧时点</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>旧基础户标识</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>旧有效户标识</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>新基础户标识</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>新有效户标识</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>旧基础户达标天数</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>旧有效户达标天数</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>新基础户达标天数</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>新有效户达标天数</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>账户销户</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>基础户降级_标识</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>有效户降级_标识</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>基础户降级_年日均</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>有效户降级_年日均</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>基础户升级_标识</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>有效户升级_标识</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>基础户升级_年日均</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>有效户升级_年日均</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>预计年日均</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>预警基础户</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>预警有效户</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>基础户临界</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>有效户临界</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>年日均基础户达标</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>年日均有效户达标</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>年日均基础户保持</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>年日均有效户保持</t>
         </is>
@@ -69143,42 +69155,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>预警基础户</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>
@@ -69379,42 +69391,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>预警有效户</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>
@@ -69435,42 +69447,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>基础户临界</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>
@@ -74771,42 +74783,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>有效户临界</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>

--- a/output/预警客户以及临界客户信息表.xlsx
+++ b/output/预警客户以及临界客户信息表.xlsx
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>刘羽佳</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -15479,7 +15479,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -19438,7 +19438,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -19652,7 +19652,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -20722,7 +20722,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -20936,7 +20936,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -22220,7 +22220,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -22327,7 +22327,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -22969,7 +22969,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -23825,7 +23825,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -24146,7 +24146,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -24253,7 +24253,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -24574,7 +24574,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -25644,7 +25644,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -26928,7 +26928,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -27984,7 +27984,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -28519,7 +28519,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -29375,7 +29375,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -32157,7 +32157,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -32585,7 +32585,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -35902,7 +35902,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -36009,7 +36009,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D333" t="n">
@@ -36330,7 +36330,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D336" t="n">
@@ -36758,7 +36758,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D340" t="n">
@@ -38256,7 +38256,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -39968,7 +39968,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -40396,7 +40396,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -41359,7 +41359,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D383" t="n">
@@ -41894,7 +41894,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D388" t="n">
@@ -42201,7 +42201,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D391" t="n">
@@ -42950,7 +42950,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D398" t="n">
@@ -43271,7 +43271,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -43378,7 +43378,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D402" t="n">
@@ -44020,7 +44020,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D408" t="n">
@@ -45076,7 +45076,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D418" t="n">
@@ -45504,7 +45504,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D422" t="n">
@@ -45718,7 +45718,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D424" t="n">
@@ -45825,7 +45825,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D425" t="n">
@@ -46146,7 +46146,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D428" t="n">
@@ -46253,7 +46253,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D429" t="n">
@@ -46360,7 +46360,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D430" t="n">
@@ -46895,7 +46895,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D435" t="n">
@@ -47430,7 +47430,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D440" t="n">
@@ -47965,7 +47965,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -48500,7 +48500,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D450" t="n">
@@ -48928,7 +48928,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D454" t="n">
@@ -49998,7 +49998,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D464" t="n">
@@ -50105,7 +50105,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D465" t="n">
@@ -50426,7 +50426,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D468" t="n">
@@ -50640,7 +50640,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D470" t="n">
@@ -50854,7 +50854,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D472" t="n">
@@ -51603,7 +51603,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D479" t="n">
@@ -51817,7 +51817,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D481" t="n">
@@ -52031,7 +52031,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D483" t="n">
@@ -52138,7 +52138,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -52352,7 +52352,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D486" t="n">
@@ -53422,7 +53422,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D496" t="n">
@@ -53529,7 +53529,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D497" t="n">
@@ -53636,7 +53636,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D498" t="n">
@@ -55027,7 +55027,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D511" t="n">
@@ -55241,7 +55241,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D513" t="n">
@@ -55348,7 +55348,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D514" t="n">
@@ -56311,7 +56311,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D523" t="n">
@@ -56525,7 +56525,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D525" t="n">
@@ -57595,7 +57595,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D535" t="n">
@@ -57702,7 +57702,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D536" t="n">
@@ -57809,7 +57809,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D537" t="n">
@@ -58237,7 +58237,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="D541" t="n">
@@ -58558,7 +58558,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D544" t="n">
@@ -59628,7 +59628,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D554" t="n">
@@ -59735,7 +59735,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D555" t="n">
@@ -59842,7 +59842,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D556" t="n">
@@ -59949,7 +59949,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D557" t="n">
@@ -60056,7 +60056,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D558" t="n">
@@ -60163,7 +60163,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D559" t="n">
@@ -61019,7 +61019,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D567" t="n">
@@ -61768,7 +61768,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D574" t="n">
@@ -61875,7 +61875,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D575" t="n">
@@ -63159,7 +63159,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D587" t="n">
@@ -63373,7 +63373,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D589" t="n">
@@ -63587,7 +63587,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D591" t="n">
@@ -64015,7 +64015,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D595" t="n">
@@ -64122,7 +64122,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D596" t="n">
@@ -65299,7 +65299,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D607" t="n">
@@ -67760,7 +67760,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D630" t="n">
@@ -69521,7 +69521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>河北益植商贸有限公司</t>
+          <t>石家庄赛丝科技有限公司</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -69530,28 +69530,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>136861.36</v>
+        <v>562360.88</v>
       </c>
       <c r="D4" t="n">
-        <v>226214.13</v>
+        <v>499299.47</v>
       </c>
       <c r="E4" t="n">
-        <v>279079.05</v>
+        <v>412120.9</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>-952577.96</v>
+        <v>-2997217.19</v>
       </c>
       <c r="H4" t="n">
-        <v>2687422.04</v>
+        <v>642782.8100000002</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>石家庄赛丝科技有限公司</t>
+          <t>山东斯邦戈商贸有限公司</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -69560,28 +69560,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>562360.88</v>
+        <v>27194.08</v>
       </c>
       <c r="D5" t="n">
-        <v>499299.47</v>
+        <v>78164.8</v>
       </c>
       <c r="E5" t="n">
-        <v>412120.9</v>
+        <v>78164.8</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>-2997217.19</v>
+        <v>284681.6</v>
       </c>
       <c r="H5" t="n">
-        <v>642782.8100000002</v>
+        <v>3924681.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>山东斯邦戈商贸有限公司</t>
+          <t>元氏县尚威贸易有限公司</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -69590,28 +69590,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27194.08</v>
+        <v>898560.33</v>
       </c>
       <c r="D6" t="n">
-        <v>78164.8</v>
+        <v>169143.27</v>
       </c>
       <c r="E6" t="n">
-        <v>78164.8</v>
+        <v>706075.28</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>284681.6</v>
+        <v>-980078.1699999999</v>
       </c>
       <c r="H6" t="n">
-        <v>3924681.6</v>
+        <v>2659921.83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>石家庄敏成建筑信息咨询有限公司</t>
+          <t>石家庄居然丽居装饰材料有限公司</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -69620,28 +69620,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1842328.5</v>
+        <v>4543396.24</v>
       </c>
       <c r="D7" t="n">
-        <v>2448805.38</v>
+        <v>3892614.36</v>
       </c>
       <c r="E7" t="n">
-        <v>54167.61</v>
+        <v>2931031.81</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>-16285805.27</v>
+        <v>-29269332.33</v>
       </c>
       <c r="H7" t="n">
-        <v>-12645805.27</v>
+        <v>-25629332.33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>石家庄居然丽居装饰材料有限公司</t>
+          <t>石家庄敏成建筑信息咨询有限公司</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -69650,28 +69650,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4543396.24</v>
+        <v>1842328.5</v>
       </c>
       <c r="D8" t="n">
-        <v>3892614.36</v>
+        <v>2448805.38</v>
       </c>
       <c r="E8" t="n">
-        <v>2931031.81</v>
+        <v>54167.61</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>-29269332.33</v>
+        <v>-16285805.27</v>
       </c>
       <c r="H8" t="n">
-        <v>-25629332.33</v>
+        <v>-12645805.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>元氏县尚威贸易有限公司</t>
+          <t>河北益植商贸有限公司</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -69680,28 +69680,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>898560.33</v>
+        <v>136861.36</v>
       </c>
       <c r="D9" t="n">
-        <v>169143.27</v>
+        <v>226214.13</v>
       </c>
       <c r="E9" t="n">
-        <v>706075.28</v>
+        <v>279079.05</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>-980078.1699999999</v>
+        <v>-952577.96</v>
       </c>
       <c r="H9" t="n">
-        <v>2659921.83</v>
+        <v>2687422.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>河北金怡化纤有限公司</t>
+          <t>河北中汇纺织有限公司</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -69710,28 +69710,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>141747.53</v>
+        <v>291010</v>
       </c>
       <c r="D10" t="n">
-        <v>69702.14</v>
+        <v>250434.81</v>
       </c>
       <c r="E10" t="n">
-        <v>977.5</v>
+        <v>22110.25</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>421107.52</v>
+        <v>-865153.9199999999</v>
       </c>
       <c r="H10" t="n">
-        <v>4061107.52</v>
+        <v>2774846.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司郑州第二分公司</t>
+          <t>解放时代新能源科技有限公司深圳分公司</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -69740,28 +69740,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>140341.9</v>
+        <v>41821.79</v>
       </c>
       <c r="D11" t="n">
-        <v>91634.03</v>
+        <v>369183.26</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>414168.36</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>268561.79</v>
+        <v>-2088451.18</v>
       </c>
       <c r="H11" t="n">
-        <v>3908561.79</v>
+        <v>1551548.82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>河北仟宏讯恒建筑工程有限公司</t>
+          <t>河北仁恒工程管理服务有限公司</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -69770,28 +69770,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>172758.08</v>
       </c>
       <c r="D12" t="n">
-        <v>117067.84</v>
+        <v>82215.39999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1191.54</v>
+        <v>82952.86</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>89333.58000000003</v>
+        <v>251539.34</v>
       </c>
       <c r="H12" t="n">
-        <v>3729333.58</v>
+        <v>3891539.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>新誉轨道（石家庄）智能交通技术有限公司</t>
+          <t>河北梵州信息技术有限公司</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -69800,28 +69800,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7732.1</v>
+        <v>344989.03</v>
       </c>
       <c r="D13" t="n">
-        <v>179969.42</v>
+        <v>283824.22</v>
       </c>
       <c r="E13" t="n">
-        <v>401236.64</v>
+        <v>279463.96</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>-751022.5800000001</v>
+        <v>-1356233.5</v>
       </c>
       <c r="H13" t="n">
-        <v>2888977.42</v>
+        <v>2283766.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>河北萌晟瑞宠科技有限公司</t>
+          <t>围场满族蒙古族自治县阳洁光伏发电有限责任公司</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -69830,28 +69830,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>3541924.69</v>
       </c>
       <c r="D14" t="n">
-        <v>77407.8</v>
+        <v>3979223.94</v>
       </c>
       <c r="E14" t="n">
-        <v>84551</v>
+        <v>3979223.94</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>283594.4</v>
+        <v>-30923791.52</v>
       </c>
       <c r="H14" t="n">
-        <v>3923594.4</v>
+        <v>-27283791.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>石家庄市申东商贸有限公司</t>
+          <t>河北钢铁产业转型升级母基金（有限合伙）</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -69860,28 +69860,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>537938.5</v>
+        <v>4519727.98</v>
       </c>
       <c r="D15" t="n">
-        <v>545970.4399999999</v>
+        <v>4527721.97</v>
       </c>
       <c r="E15" t="n">
-        <v>505762.15</v>
+        <v>4527721.97</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>-3417555.23</v>
+        <v>-35311775.76</v>
       </c>
       <c r="H15" t="n">
-        <v>222444.7700000003</v>
+        <v>-31671775.76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>河北微婶餐饮服务有限公司</t>
+          <t>新誉轨道（石家庄）智能交通技术有限公司</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -69890,28 +69890,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>315751.67</v>
+        <v>7732.1</v>
       </c>
       <c r="D16" t="n">
-        <v>183443.14</v>
+        <v>179969.42</v>
       </c>
       <c r="E16" t="n">
-        <v>44054.31</v>
+        <v>401236.64</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>-418156.2900000001</v>
+        <v>-751022.5800000001</v>
       </c>
       <c r="H16" t="n">
-        <v>3221843.71</v>
+        <v>2888977.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>廊坊隆冀达金属零部件有限公司</t>
+          <t>河北璞昱科技有限公司</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -69920,28 +69920,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>652679.54</v>
+        <v>111367.7</v>
       </c>
       <c r="D17" t="n">
-        <v>6930266.93</v>
+        <v>151289.62</v>
       </c>
       <c r="E17" t="n">
-        <v>9091788.08</v>
+        <v>149915.38</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>-56693656.59</v>
+        <v>-298942.72</v>
       </c>
       <c r="H17" t="n">
-        <v>-53053656.59</v>
+        <v>3341057.28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>河北钢铁产业转型升级母基金（有限合伙）</t>
+          <t>秦皇岛发源建材装饰工程有限公司</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -69950,28 +69950,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4519727.98</v>
+        <v>18933.13</v>
       </c>
       <c r="D18" t="n">
-        <v>4527721.97</v>
+        <v>51202.39</v>
       </c>
       <c r="E18" t="n">
-        <v>4527721.97</v>
+        <v>11028.2</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>-35311775.76</v>
+        <v>540555.0700000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-31671775.76</v>
+        <v>4180555.07</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司深圳分公司</t>
+          <t>石家庄市申东商贸有限公司</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -69980,28 +69980,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>41821.79</v>
+        <v>537938.5</v>
       </c>
       <c r="D19" t="n">
-        <v>369183.26</v>
+        <v>545970.4399999999</v>
       </c>
       <c r="E19" t="n">
-        <v>414168.36</v>
+        <v>505762.15</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>-2088451.18</v>
+        <v>-3417555.23</v>
       </c>
       <c r="H19" t="n">
-        <v>1551548.82</v>
+        <v>222444.7700000003</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>河北世鸿餐饮管理有限公司</t>
+          <t>河北微婶餐饮服务有限公司</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -70010,28 +70010,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>177304.59</v>
+        <v>315751.67</v>
       </c>
       <c r="D20" t="n">
-        <v>84310.64</v>
+        <v>183443.14</v>
       </c>
       <c r="E20" t="n">
-        <v>9295.639999999999</v>
+        <v>44054.31</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>310529.88</v>
+        <v>-418156.2900000001</v>
       </c>
       <c r="H20" t="n">
-        <v>3950529.88</v>
+        <v>3221843.71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>河北新华科极兽药集团有限公司</t>
+          <t>廊坊隆冀达金属零部件有限公司</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -70040,28 +70040,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>83449.44</v>
+        <v>652679.54</v>
       </c>
       <c r="D21" t="n">
-        <v>432722.53</v>
+        <v>6930266.93</v>
       </c>
       <c r="E21" t="n">
-        <v>96.84999999999999</v>
+        <v>9091788.08</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>-2119154.56</v>
+        <v>-56693656.59</v>
       </c>
       <c r="H21" t="n">
-        <v>1520845.44</v>
+        <v>-53053656.59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>西藏汇科华药业有限公司</t>
+          <t>河北康卫仕医疗科技有限公司</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -70070,28 +70070,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13739639.99</v>
+        <v>123958.77</v>
       </c>
       <c r="D22" t="n">
-        <v>17339236.62</v>
+        <v>155374.76</v>
       </c>
       <c r="E22" t="n">
-        <v>15487720.18</v>
+        <v>74026.00999999999</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>-135952376.52</v>
+        <v>-251649.3300000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-132312376.52</v>
+        <v>3388350.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>全缆电缆集团有限公司</t>
+          <t>石家庄企合科技有限公司</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -70100,28 +70100,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>163485.62</v>
+        <v>211284.44</v>
       </c>
       <c r="D23" t="n">
-        <v>163453.09</v>
+        <v>316241.34</v>
       </c>
       <c r="E23" t="n">
-        <v>163453.09</v>
+        <v>369312.53</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>-397624.7199999999</v>
+        <v>-1673001.91</v>
       </c>
       <c r="H23" t="n">
-        <v>3242375.28</v>
+        <v>1966998.09</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>河北中汇纺织有限公司</t>
+          <t>河北春鼎物业管理有限公司</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -70130,28 +70130,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>291010</v>
+        <v>36868.67</v>
       </c>
       <c r="D24" t="n">
-        <v>250434.81</v>
+        <v>52439.35</v>
       </c>
       <c r="E24" t="n">
-        <v>22110.25</v>
+        <v>53950.3</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>-865153.9199999999</v>
+        <v>488974.2500000001</v>
       </c>
       <c r="H24" t="n">
-        <v>2774846.08</v>
+        <v>4128974.25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>永通中策电缆科技有限公司</t>
+          <t>解放时代新能源科技有限公司苏州分公司</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -70160,28 +70160,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>199901.44</v>
+        <v>338512.85</v>
       </c>
       <c r="D25" t="n">
-        <v>247282.89</v>
+        <v>341782.26</v>
       </c>
       <c r="E25" t="n">
-        <v>247282.89</v>
+        <v>426661</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>-1068263.12</v>
+        <v>-1909136.82</v>
       </c>
       <c r="H25" t="n">
-        <v>2571736.88</v>
+        <v>1730863.18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>石家庄华北盛德贸易有限公司</t>
+          <t>河北富众未来科技有限公司</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -70190,28 +70190,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>152975.49</v>
+        <v>446458.58</v>
       </c>
       <c r="D26" t="n">
-        <v>66364.3</v>
+        <v>291418.17</v>
       </c>
       <c r="E26" t="n">
-        <v>5428.47</v>
+        <v>26525.42</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>440021.4300000001</v>
+        <v>-1156452.61</v>
       </c>
       <c r="H26" t="n">
-        <v>4080021.43</v>
+        <v>2483547.39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>围场满族蒙古族自治县阳洁光伏发电有限责任公司</t>
+          <t>河北新华科极兽药集团有限公司</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -70220,28 +70220,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3541924.69</v>
+        <v>83449.44</v>
       </c>
       <c r="D27" t="n">
-        <v>3979223.94</v>
+        <v>432722.53</v>
       </c>
       <c r="E27" t="n">
-        <v>3979223.94</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>-30923791.52</v>
+        <v>-2119154.56</v>
       </c>
       <c r="H27" t="n">
-        <v>-27283791.52</v>
+        <v>1520845.44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>河北嘉庭旺生物科技有限公司</t>
+          <t>石家庄华北盛德贸易有限公司</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -70250,28 +70250,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2154867.97</v>
+        <v>152975.49</v>
       </c>
       <c r="D28" t="n">
-        <v>2759563.96</v>
+        <v>66364.3</v>
       </c>
       <c r="E28" t="n">
-        <v>2639127.97</v>
+        <v>5428.47</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>-21046075.69</v>
+        <v>440021.4300000001</v>
       </c>
       <c r="H28" t="n">
-        <v>-17406075.69</v>
+        <v>4080021.43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>河北富众未来科技有限公司</t>
+          <t>永通中策电缆科技有限公司</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -70280,28 +70280,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>446458.58</v>
+        <v>199901.44</v>
       </c>
       <c r="D29" t="n">
-        <v>291418.17</v>
+        <v>247282.89</v>
       </c>
       <c r="E29" t="n">
-        <v>26525.42</v>
+        <v>247282.89</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>-1156452.61</v>
+        <v>-1068263.12</v>
       </c>
       <c r="H29" t="n">
-        <v>2483547.39</v>
+        <v>2571736.88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司苏州分公司</t>
+          <t>石家庄市陆升水处理设备有限公司</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -70310,28 +70310,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>338512.85</v>
+        <v>128169.9</v>
       </c>
       <c r="D30" t="n">
-        <v>341782.26</v>
+        <v>82160.38</v>
       </c>
       <c r="E30" t="n">
-        <v>426661</v>
+        <v>5275.41</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>-1909136.82</v>
+        <v>329601.93</v>
       </c>
       <c r="H30" t="n">
-        <v>1730863.18</v>
+        <v>3969601.93</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>河北璞昱科技有限公司</t>
+          <t>合一智慧物流服务（河北）有限公司</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -70340,28 +70340,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>111367.7</v>
+        <v>103827.62</v>
       </c>
       <c r="D31" t="n">
-        <v>151289.62</v>
+        <v>884737.75</v>
       </c>
       <c r="E31" t="n">
-        <v>149915.38</v>
+        <v>1959463.61</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>-298942.72</v>
+        <v>-7242627.86</v>
       </c>
       <c r="H31" t="n">
-        <v>3341057.28</v>
+        <v>-3602627.86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司成都分公司</t>
+          <t>西藏汇科华药业有限公司</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -70370,28 +70370,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>322920.74</v>
+        <v>13739639.99</v>
       </c>
       <c r="D32" t="n">
-        <v>1183251.82</v>
+        <v>17339236.62</v>
       </c>
       <c r="E32" t="n">
-        <v>1146833</v>
+        <v>15487720.18</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>-8519595.74</v>
+        <v>-135952376.52</v>
       </c>
       <c r="H32" t="n">
-        <v>-4879595.74</v>
+        <v>-132312376.52</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>河北产投基石氢能产业投资基金合伙企业（有限合伙）</t>
+          <t>全缆电缆集团有限公司</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -70400,28 +70400,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6992752.8</v>
+        <v>163485.62</v>
       </c>
       <c r="D33" t="n">
-        <v>4945344.22</v>
+        <v>163453.09</v>
       </c>
       <c r="E33" t="n">
-        <v>4945344.22</v>
+        <v>163453.09</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>-38652753.76</v>
+        <v>-397624.7199999999</v>
       </c>
       <c r="H33" t="n">
-        <v>-35012753.76</v>
+        <v>3242375.28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司天津分公司</t>
+          <t>河北益丰生物医药有限公司</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -70430,28 +70430,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3211.11</v>
+        <v>543809.28</v>
       </c>
       <c r="D34" t="n">
-        <v>105529.64</v>
+        <v>284463.57</v>
       </c>
       <c r="E34" t="n">
-        <v>49073.74</v>
+        <v>246166.78</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>122218.78</v>
+        <v>-1327411.77</v>
       </c>
       <c r="H34" t="n">
-        <v>3762218.78</v>
+        <v>2312588.23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司哈密分公司</t>
+          <t>石家庄横琴企业管理有限公司</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -70460,28 +70460,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>25021.59</v>
+        <v>189997.22</v>
       </c>
       <c r="D35" t="n">
-        <v>650761.96</v>
+        <v>320236.48</v>
       </c>
       <c r="E35" t="n">
-        <v>209979</v>
+        <v>294184.74</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>-3855312.72</v>
+        <v>-1625840.1</v>
       </c>
       <c r="H35" t="n">
-        <v>-215312.7199999996</v>
+        <v>2014159.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>河北鸿联九五信息产业有限公司邯郸分公司</t>
+          <t>河北世鸿餐饮管理有限公司</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -70490,28 +70490,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>18621.39</v>
+        <v>177304.59</v>
       </c>
       <c r="D36" t="n">
-        <v>86716.37</v>
+        <v>84310.64</v>
       </c>
       <c r="E36" t="n">
-        <v>6493.52</v>
+        <v>9295.639999999999</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>296491.89</v>
+        <v>310529.88</v>
       </c>
       <c r="H36" t="n">
-        <v>3936491.89</v>
+        <v>3950529.88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司青岛第二分公司</t>
+          <t>河北益安诚人力资源服务有限公司</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -70520,28 +70520,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>13531.06</v>
+        <v>2387702.52</v>
       </c>
       <c r="D37" t="n">
-        <v>371286.67</v>
+        <v>2380909.83</v>
       </c>
       <c r="E37" t="n">
-        <v>461984</v>
+        <v>2263042.01</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>-2150990.69</v>
+        <v>-18019410.82</v>
       </c>
       <c r="H37" t="n">
-        <v>1489009.31</v>
+        <v>-14379410.82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司合肥分公司</t>
+          <t>解放时代新能源科技有限公司青岛分公司</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -70550,28 +70550,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6479.04</v>
+        <v>429151.01</v>
       </c>
       <c r="D38" t="n">
-        <v>121177.79</v>
+        <v>1395285.85</v>
       </c>
       <c r="E38" t="n">
-        <v>269359.34</v>
+        <v>1837139</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>-207603.8699999999</v>
+        <v>-10694139.95</v>
       </c>
       <c r="H38" t="n">
-        <v>3432396.13</v>
+        <v>-7054139.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司南昌分公司</t>
+          <t>解放时代新能源科技有限公司青岛第二分公司</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -70580,28 +70580,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>21632.3</v>
+        <v>13531.06</v>
       </c>
       <c r="D39" t="n">
-        <v>64159.42</v>
+        <v>371286.67</v>
       </c>
       <c r="E39" t="n">
-        <v>149004</v>
+        <v>461984</v>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>311880.0600000001</v>
+        <v>-2150990.69</v>
       </c>
       <c r="H39" t="n">
-        <v>3951880.06</v>
+        <v>1489009.31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司张家口分公司</t>
+          <t>解放时代新能源科技有限公司天津分公司</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -70610,28 +70610,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12462.54</v>
+        <v>3211.11</v>
       </c>
       <c r="D40" t="n">
-        <v>177817.52</v>
+        <v>105529.64</v>
       </c>
       <c r="E40" t="n">
-        <v>214985</v>
+        <v>49073.74</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>-549707.6399999999</v>
+        <v>122218.78</v>
       </c>
       <c r="H40" t="n">
-        <v>3090292.36</v>
+        <v>3762218.78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司厦门分公司</t>
+          <t>河北产投基石氢能产业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -70640,28 +70640,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>377969.83</v>
+        <v>6992752.8</v>
       </c>
       <c r="D41" t="n">
-        <v>1073757.95</v>
+        <v>4945344.22</v>
       </c>
       <c r="E41" t="n">
-        <v>637326.78</v>
+        <v>4945344.22</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>-7243632.430000001</v>
+        <v>-38652753.76</v>
       </c>
       <c r="H41" t="n">
-        <v>-3603632.43</v>
+        <v>-35012753.76</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司临汾分公司</t>
+          <t>河北鸿联九五信息产业有限公司邯郸分公司</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -70670,28 +70670,28 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>87405.13</v>
+        <v>18621.39</v>
       </c>
       <c r="D42" t="n">
-        <v>303138.65</v>
+        <v>86716.37</v>
       </c>
       <c r="E42" t="n">
-        <v>183786</v>
+        <v>6493.52</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>-1395756.55</v>
+        <v>296491.89</v>
       </c>
       <c r="H42" t="n">
-        <v>2244243.45</v>
+        <v>3936491.89</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司贵阳分公司</t>
+          <t>解放时代新能源科技有限公司哈密分公司</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -70700,28 +70700,28 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>39465.16</v>
+        <v>25021.59</v>
       </c>
       <c r="D43" t="n">
-        <v>366704.36</v>
+        <v>650761.96</v>
       </c>
       <c r="E43" t="n">
-        <v>526758.66</v>
+        <v>209979</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>-2183689.18</v>
+        <v>-3855312.72</v>
       </c>
       <c r="H43" t="n">
-        <v>1456310.82</v>
+        <v>-215312.7199999996</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司武汉分公司</t>
+          <t>解放时代新能源科技有限公司南昌分公司</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -70730,28 +70730,28 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>87027.59</v>
+        <v>21632.3</v>
       </c>
       <c r="D44" t="n">
-        <v>299891.07</v>
+        <v>64159.42</v>
       </c>
       <c r="E44" t="n">
-        <v>84070.60000000001</v>
+        <v>149004</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>-1273308.09</v>
+        <v>311880.0600000001</v>
       </c>
       <c r="H44" t="n">
-        <v>2366691.91</v>
+        <v>3951880.06</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司青岛分公司</t>
+          <t>河北文轩贸易有限公司</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -70760,22 +70760,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>429151.01</v>
+        <v>620898.98</v>
       </c>
       <c r="D45" t="n">
-        <v>1395285.85</v>
+        <v>4282108.85</v>
       </c>
       <c r="E45" t="n">
-        <v>1837139</v>
+        <v>93739.86</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>-10694139.95</v>
+        <v>-29158501.81</v>
       </c>
       <c r="H45" t="n">
-        <v>-7054139.95</v>
+        <v>-25518501.81</v>
       </c>
     </row>
     <row r="46">
@@ -70811,7 +70811,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司长沙分公司</t>
+          <t>河北文通国际贸易有限公司</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -70820,28 +70820,28 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>196087.3</v>
+        <v>5172907.01</v>
       </c>
       <c r="D47" t="n">
-        <v>212350.57</v>
+        <v>5190279.6</v>
       </c>
       <c r="E47" t="n">
-        <v>8190.8</v>
+        <v>5190279.6</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>-584644.79</v>
+        <v>-40612236.8</v>
       </c>
       <c r="H47" t="n">
-        <v>3055355.21</v>
+        <v>-36972236.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司湖州分公司</t>
+          <t>河北金怡化纤有限公司</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -70850,28 +70850,28 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>644284.63</v>
+        <v>141747.53</v>
       </c>
       <c r="D48" t="n">
-        <v>1391105.26</v>
+        <v>69702.14</v>
       </c>
       <c r="E48" t="n">
-        <v>1806563</v>
+        <v>977.5</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>-10634299.82</v>
+        <v>421107.52</v>
       </c>
       <c r="H48" t="n">
-        <v>-6994299.82</v>
+        <v>4061107.52</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司西安分公司</t>
+          <t>解放时代新能源科技有限公司贵阳分公司</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -70880,538 +70880,538 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>179130.96</v>
+        <v>39465.16</v>
       </c>
       <c r="D49" t="n">
-        <v>293936.97</v>
+        <v>366704.36</v>
       </c>
       <c r="E49" t="n">
-        <v>187469.9</v>
+        <v>526758.66</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>-1335028.69</v>
+        <v>-2183689.18</v>
       </c>
       <c r="H49" t="n">
-        <v>2304971.31</v>
+        <v>1456310.82</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>石家庄顺合信息咨询服务有限公司</t>
+          <t>石家庄铭派机电有限公司</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>134600.17</v>
+        <v>855166.83</v>
       </c>
       <c r="D50" t="n">
-        <v>119087.91</v>
+        <v>1055659.03</v>
       </c>
       <c r="E50" t="n">
-        <v>227035.83</v>
+        <v>1326606.98</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>-150651.2</v>
+        <v>-7806220.190000001</v>
       </c>
       <c r="H50" t="n">
-        <v>3489348.8</v>
+        <v>-4166220.190000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>新疆燕翔实业发展有限公司</t>
+          <t>解放时代新能源科技有限公司郑州第二分公司</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>134066.34</v>
+        <v>140341.9</v>
       </c>
       <c r="D51" t="n">
-        <v>94220.10000000001</v>
+        <v>91634.03</v>
       </c>
       <c r="E51" t="n">
-        <v>140748.79</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>109710.51</v>
+        <v>268561.79</v>
       </c>
       <c r="H51" t="n">
-        <v>3749710.51</v>
+        <v>3908561.79</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>河北融腾人力资源服务有限公司</t>
+          <t>河北仟宏讯恒建筑工程有限公司</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>451928.11</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>707815.83</v>
+        <v>117067.84</v>
       </c>
       <c r="E52" t="n">
-        <v>676969.39</v>
+        <v>1191.54</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>-4721680.199999999</v>
+        <v>89333.58000000003</v>
       </c>
       <c r="H52" t="n">
-        <v>-1081680.199999999</v>
+        <v>3729333.58</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>河北宇腾瑞元科技有限公司</t>
+          <t>河北萌晟瑞宠科技有限公司</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>349207.39</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>242175.49</v>
+        <v>77407.8</v>
       </c>
       <c r="E53" t="n">
-        <v>13852.62</v>
+        <v>84551</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>-799081.05</v>
+        <v>283594.4</v>
       </c>
       <c r="H53" t="n">
-        <v>2840918.95</v>
+        <v>3923594.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>石家庄普勤停车服务有限公司</t>
+          <t>河北图佳智联科技有限公司</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>128094.32</v>
+        <v>317501.33</v>
       </c>
       <c r="D54" t="n">
-        <v>263724.38</v>
+        <v>269454.77</v>
       </c>
       <c r="E54" t="n">
-        <v>59176.95</v>
+        <v>265467.29</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>-995247.6100000001</v>
+        <v>-1241650.68</v>
       </c>
       <c r="H54" t="n">
-        <v>2644752.39</v>
+        <v>2398349.32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>河北莱拓生物科技有限公司</t>
+          <t>解放时代新能源科技有限公司合肥分公司</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8118.28</v>
+        <v>6479.04</v>
       </c>
       <c r="D55" t="n">
-        <v>83970.38</v>
+        <v>121177.79</v>
       </c>
       <c r="E55" t="n">
-        <v>78993.07000000001</v>
+        <v>269359.34</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>243214.27</v>
+        <v>-207603.8699999999</v>
       </c>
       <c r="H55" t="n">
-        <v>3883214.27</v>
+        <v>3432396.13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>河北加贝商贸有限公司</t>
+          <t>河北嘉庭旺生物科技有限公司</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>140934.44</v>
+        <v>2154867.97</v>
       </c>
       <c r="D56" t="n">
-        <v>127191.99</v>
+        <v>2759563.96</v>
       </c>
       <c r="E56" t="n">
-        <v>10214.34</v>
+        <v>2639127.97</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>9441.729999999927</v>
+        <v>-21046075.69</v>
       </c>
       <c r="H56" t="n">
-        <v>3649441.73</v>
+        <v>-17406075.69</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>中科电谷（北京）系统技术有限公司</t>
+          <t>解放时代新能源科技有限公司武汉分公司</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>230338.19</v>
+        <v>87027.59</v>
       </c>
       <c r="D57" t="n">
-        <v>74779.23</v>
+        <v>299891.07</v>
       </c>
       <c r="E57" t="n">
-        <v>1061777.01</v>
+        <v>84070.60000000001</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>-675231.62</v>
+        <v>-1273308.09</v>
       </c>
       <c r="H57" t="n">
-        <v>2964768.38</v>
+        <v>2366691.91</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>河北昂克电子工程技术有限公司</t>
+          <t>解放时代新能源科技有限公司西安分公司</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>42599.72</v>
+        <v>179130.96</v>
       </c>
       <c r="D58" t="n">
-        <v>192258.65</v>
+        <v>293936.97</v>
       </c>
       <c r="E58" t="n">
-        <v>192350.74</v>
+        <v>187469.9</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>-628161.29</v>
+        <v>-1335028.69</v>
       </c>
       <c r="H58" t="n">
-        <v>3011838.71</v>
+        <v>2304971.31</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>河北衡湖创业投资基金合伙企业（有限合伙）</t>
+          <t>解放时代新能源科技有限公司张家口分公司</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>12462.54</v>
       </c>
       <c r="D59" t="n">
-        <v>34556376.81</v>
+        <v>177817.52</v>
       </c>
       <c r="E59" t="n">
-        <v>80800000</v>
+        <v>214985</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>-321784637.67</v>
+        <v>-549707.6399999999</v>
       </c>
       <c r="H59" t="n">
-        <v>-318144637.67</v>
+        <v>3090292.36</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>嘉兴中玮股权投资合伙企业(有限合伙)</t>
+          <t>解放时代新能源科技有限公司长沙分公司</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>196087.3</v>
       </c>
       <c r="D60" t="n">
-        <v>6211304.35</v>
+        <v>212350.57</v>
       </c>
       <c r="E60" t="n">
-        <v>10000</v>
+        <v>8190.8</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>-42579130.45</v>
+        <v>-584644.79</v>
       </c>
       <c r="H60" t="n">
-        <v>-38939130.45</v>
+        <v>3055355.21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>石家庄骋朴科技有限责任公司</t>
+          <t>解放时代新能源科技有限公司湖州分公司</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>16270.6</v>
+        <v>644284.63</v>
       </c>
       <c r="D61" t="n">
-        <v>332271.04</v>
+        <v>1391105.26</v>
       </c>
       <c r="E61" t="n">
-        <v>222636.14</v>
+        <v>1806563</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>-1638533.42</v>
+        <v>-10634299.82</v>
       </c>
       <c r="H61" t="n">
-        <v>2001466.58</v>
+        <v>-6994299.82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>河北师达教育科技有限公司</t>
+          <t>解放时代新能源科技有限公司成都分公司</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>101409.27</v>
+        <v>322920.74</v>
       </c>
       <c r="D62" t="n">
-        <v>100903.21</v>
+        <v>1183251.82</v>
       </c>
       <c r="E62" t="n">
-        <v>100903.21</v>
+        <v>1146833</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>102774.32</v>
+        <v>-8519595.74</v>
       </c>
       <c r="H62" t="n">
-        <v>3742774.32</v>
+        <v>-4879595.74</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>石家庄德色特商贸有限公司</t>
+          <t>石家庄健牛科技有限公司</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>245521.24</v>
+        <v>124580.27</v>
       </c>
       <c r="D63" t="n">
-        <v>266828.62</v>
+        <v>169460.46</v>
       </c>
       <c r="E63" t="n">
-        <v>307278.87</v>
+        <v>105541.79</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>-1265079.21</v>
+        <v>-381765.0099999999</v>
       </c>
       <c r="H63" t="n">
-        <v>2374920.79</v>
+        <v>3258234.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>石家庄卓禾房地产经纪有限公司</t>
+          <t>解放时代新能源科技有限公司临汾分公司</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>76236.44</v>
+        <v>87405.13</v>
       </c>
       <c r="D64" t="n">
-        <v>66575.45</v>
+        <v>303138.65</v>
       </c>
       <c r="E64" t="n">
-        <v>47014.64</v>
+        <v>183786</v>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>396957.21</v>
+        <v>-1395756.55</v>
       </c>
       <c r="H64" t="n">
-        <v>4036957.21</v>
+        <v>2244243.45</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>石家庄尊唯体育科技有限公司</t>
+          <t>解放时代新能源科技有限公司厦门分公司</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>308627.62</v>
+        <v>377969.83</v>
       </c>
       <c r="D65" t="n">
-        <v>478745.72</v>
+        <v>1073757.95</v>
       </c>
       <c r="E65" t="n">
-        <v>290383.12</v>
+        <v>637326.78</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>-2731603.16</v>
+        <v>-7243632.430000001</v>
       </c>
       <c r="H65" t="n">
-        <v>908396.8400000002</v>
+        <v>-3603632.43</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>河北桥牌体育发展有限公司</t>
+          <t>河北博斯特展览服务有限公司</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>218568.32</v>
+        <v>273867.56</v>
       </c>
       <c r="D66" t="n">
-        <v>112652.29</v>
+        <v>73759.55</v>
       </c>
       <c r="E66" t="n">
-        <v>94107.32000000001</v>
+        <v>201805.43</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>27326.65000000001</v>
+        <v>191877.72</v>
       </c>
       <c r="H66" t="n">
-        <v>3667326.65</v>
+        <v>3831877.72</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>河北溯瞬信息科技有限公司</t>
+          <t>石家庄顺合信息咨询服务有限公司</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -71420,28 +71420,28 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>85475.78</v>
+        <v>134600.17</v>
       </c>
       <c r="D67" t="n">
-        <v>1423332.14</v>
+        <v>119087.91</v>
       </c>
       <c r="E67" t="n">
-        <v>100317.94</v>
+        <v>227035.83</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>-9153642.92</v>
+        <v>-150651.2</v>
       </c>
       <c r="H67" t="n">
-        <v>-5513642.92</v>
+        <v>3489348.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>河北佰汀商贸有限公司</t>
+          <t>河北溯瞬信息科技有限公司</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -71450,28 +71450,28 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>655363.9399999999</v>
+        <v>85475.78</v>
       </c>
       <c r="D68" t="n">
-        <v>53932.2</v>
+        <v>1423332.14</v>
       </c>
       <c r="E68" t="n">
-        <v>417.61</v>
+        <v>100317.94</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>532056.99</v>
+        <v>-9153642.92</v>
       </c>
       <c r="H68" t="n">
-        <v>4172056.99</v>
+        <v>-5513642.92</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>石家庄水田贸易有限公司</t>
+          <t>石家庄骋朴科技有限责任公司</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -71480,28 +71480,28 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>349798.81</v>
+        <v>16270.6</v>
       </c>
       <c r="D69" t="n">
-        <v>122987.05</v>
+        <v>332271.04</v>
       </c>
       <c r="E69" t="n">
-        <v>2591.4</v>
+        <v>222636.14</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>46499.25</v>
+        <v>-1638533.42</v>
       </c>
       <c r="H69" t="n">
-        <v>3686499.25</v>
+        <v>2001466.58</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>河北睿爱文化传媒有限公司</t>
+          <t>河北加贝商贸有限公司</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -71510,28 +71510,28 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1263.27</v>
+        <v>140934.44</v>
       </c>
       <c r="D70" t="n">
-        <v>68696.83</v>
+        <v>127191.99</v>
       </c>
       <c r="E70" t="n">
-        <v>54202.3</v>
+        <v>10214.34</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>374919.89</v>
+        <v>9441.729999999927</v>
       </c>
       <c r="H70" t="n">
-        <v>4014919.89</v>
+        <v>3649441.73</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>河北周旗建筑安装有限公司</t>
+          <t>中义诚河北会计师事务所（普通合伙）</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -71540,28 +71540,28 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>16893.92</v>
+        <v>684020.15</v>
       </c>
       <c r="D71" t="n">
-        <v>92681.23</v>
+        <v>1311808.25</v>
       </c>
       <c r="E71" t="n">
-        <v>4428.55</v>
+        <v>1311808.25</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>256802.8400000001</v>
+        <v>-9584466</v>
       </c>
       <c r="H71" t="n">
-        <v>3896802.84</v>
+        <v>-5944466</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>河北博晟工程项目管理有限公司</t>
+          <t>河北莱拓生物科技有限公司</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -71570,28 +71570,28 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>171113.75</v>
+        <v>8118.28</v>
       </c>
       <c r="D72" t="n">
-        <v>220640.75</v>
+        <v>83970.38</v>
       </c>
       <c r="E72" t="n">
-        <v>158485.51</v>
+        <v>78993.07000000001</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>-792970.76</v>
+        <v>243214.27</v>
       </c>
       <c r="H72" t="n">
-        <v>2847029.24</v>
+        <v>3883214.27</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>环众市政工程（河北）有限公司</t>
+          <t>新疆燕翔实业发展有限公司</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -71600,28 +71600,28 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>13333.77</v>
+        <v>134066.34</v>
       </c>
       <c r="D73" t="n">
-        <v>112018.24</v>
+        <v>94220.10000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>2476.2</v>
+        <v>140748.79</v>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>123396.1199999999</v>
+        <v>109710.51</v>
       </c>
       <c r="H73" t="n">
-        <v>3763396.12</v>
+        <v>3749710.51</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>河北金天塑胶新材料有限公司</t>
+          <t>中科电谷（北京）系统技术有限公司</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -71630,28 +71630,28 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>87058.78</v>
+        <v>230338.19</v>
       </c>
       <c r="D74" t="n">
-        <v>102083.26</v>
+        <v>74779.23</v>
       </c>
       <c r="E74" t="n">
-        <v>133359.22</v>
+        <v>1061777.01</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>62057.96000000008</v>
+        <v>-675231.62</v>
       </c>
       <c r="H74" t="n">
-        <v>3702057.959999999</v>
+        <v>2964768.38</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>石家庄世征科技有限公司</t>
+          <t>河北衡湖创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -71660,28 +71660,28 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>74484.74000000001</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>198515.66</v>
+        <v>34556376.81</v>
       </c>
       <c r="E75" t="n">
-        <v>85482.48</v>
+        <v>80800000</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>-565092.1000000001</v>
+        <v>-321784637.67</v>
       </c>
       <c r="H75" t="n">
-        <v>3074907.9</v>
+        <v>-318144637.67</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>中义诚河北会计师事务所（普通合伙）</t>
+          <t>石家庄水田贸易有限公司</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -71690,28 +71690,28 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>684020.15</v>
+        <v>349798.81</v>
       </c>
       <c r="D76" t="n">
-        <v>1311808.25</v>
+        <v>122987.05</v>
       </c>
       <c r="E76" t="n">
-        <v>1311808.25</v>
+        <v>2591.4</v>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>-9584466</v>
+        <v>46499.25</v>
       </c>
       <c r="H76" t="n">
-        <v>-5944466</v>
+        <v>3686499.25</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>衡水宏祥桥梁工程材料科技有限公司</t>
+          <t>河北金天塑胶新材料有限公司</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -71720,28 +71720,28 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>136811.51</v>
+        <v>87058.78</v>
       </c>
       <c r="D77" t="n">
-        <v>141637.47</v>
+        <v>102083.26</v>
       </c>
       <c r="E77" t="n">
-        <v>358117.59</v>
+        <v>133359.22</v>
       </c>
       <c r="F77" t="n">
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>-439579.8800000001</v>
+        <v>62057.96000000008</v>
       </c>
       <c r="H77" t="n">
-        <v>3200420.12</v>
+        <v>3702057.959999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>石家庄磊实建材有限公司</t>
+          <t>衡水宏祥桥梁工程材料科技有限公司</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -71750,28 +71750,28 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>424736.07</v>
+        <v>136811.51</v>
       </c>
       <c r="D78" t="n">
-        <v>508089.89</v>
+        <v>141637.47</v>
       </c>
       <c r="E78" t="n">
-        <v>508089.89</v>
+        <v>358117.59</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>-3154719.120000001</v>
+        <v>-439579.8800000001</v>
       </c>
       <c r="H78" t="n">
-        <v>485280.8799999995</v>
+        <v>3200420.12</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>华艺博展装饰有限公司</t>
+          <t>石家庄德色特商贸有限公司</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -71780,28 +71780,28 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>245521.24</v>
       </c>
       <c r="D79" t="n">
-        <v>202891.45</v>
+        <v>266828.62</v>
       </c>
       <c r="E79" t="n">
-        <v>499951</v>
+        <v>307278.87</v>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>-1010191.15</v>
+        <v>-1265079.21</v>
       </c>
       <c r="H79" t="n">
-        <v>2629808.85</v>
+        <v>2374920.79</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>可帮（河北）企业管理咨询有限公司</t>
+          <t>石家庄卓禾房地产经纪有限公司</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -71810,28 +71810,28 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>998854.39</v>
+        <v>76236.44</v>
       </c>
       <c r="D80" t="n">
-        <v>1119307.06</v>
+        <v>66575.45</v>
       </c>
       <c r="E80" t="n">
-        <v>1597036.97</v>
+        <v>47014.64</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>-8522186.390000001</v>
+        <v>396957.21</v>
       </c>
       <c r="H80" t="n">
-        <v>-4882186.390000001</v>
+        <v>4036957.21</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>河北永明地质工程机械有限公司</t>
+          <t>河北睿爱文化传媒有限公司</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -71840,28 +71840,28 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8852835.34</v>
+        <v>1263.27</v>
       </c>
       <c r="D81" t="n">
-        <v>1682278.66</v>
+        <v>68696.83</v>
       </c>
       <c r="E81" t="n">
-        <v>120986.15</v>
+        <v>54202.3</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>-10986936.77</v>
+        <v>374919.89</v>
       </c>
       <c r="H81" t="n">
-        <v>-7346936.77</v>
+        <v>4014919.89</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>石家庄氐宿企业管理咨询有限公司桥西分公司</t>
+          <t>石家庄尊唯体育科技有限公司</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -71870,28 +71870,28 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>307170.35</v>
+        <v>308627.62</v>
       </c>
       <c r="D82" t="n">
-        <v>471163.98</v>
+        <v>478745.72</v>
       </c>
       <c r="E82" t="n">
-        <v>287874.26</v>
+        <v>290383.12</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>-2676022.12</v>
+        <v>-2731603.16</v>
       </c>
       <c r="H82" t="n">
-        <v>963977.8800000001</v>
+        <v>908396.8400000002</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>河北中天世纪通信技术有限公司</t>
+          <t>环众市政工程（河北）有限公司</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -71900,28 +71900,28 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>124900.95</v>
+        <v>13333.77</v>
       </c>
       <c r="D83" t="n">
-        <v>125826.19</v>
+        <v>112018.24</v>
       </c>
       <c r="E83" t="n">
-        <v>472.47</v>
+        <v>2476.2</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>28744.19999999992</v>
+        <v>123396.1199999999</v>
       </c>
       <c r="H83" t="n">
-        <v>3668744.2</v>
+        <v>3763396.12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>河北恒青电子科技有限公司</t>
+          <t>河北师达教育科技有限公司</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -71930,28 +71930,28 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>139230.75</v>
+        <v>101409.27</v>
       </c>
       <c r="D84" t="n">
-        <v>59982.81</v>
+        <v>100903.21</v>
       </c>
       <c r="E84" t="n">
-        <v>56090.87</v>
+        <v>100903.21</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>434029.46</v>
+        <v>102774.32</v>
       </c>
       <c r="H84" t="n">
-        <v>4074029.459999999</v>
+        <v>3742774.32</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>河北益途建筑机械设备租赁有限公司</t>
+          <t>河北周旗建筑安装有限公司</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -71960,28 +71960,28 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>552260.1</v>
+        <v>16893.92</v>
       </c>
       <c r="D85" t="n">
-        <v>246504.9</v>
+        <v>92681.23</v>
       </c>
       <c r="E85" t="n">
-        <v>230460.01</v>
+        <v>4428.55</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>-1045994.31</v>
+        <v>256802.8400000001</v>
       </c>
       <c r="H85" t="n">
-        <v>2594005.69</v>
+        <v>3896802.84</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>河北锅圈食汇商业管理有限公司</t>
+          <t>河北昂克电子工程技术有限公司</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -71990,28 +71990,28 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1210852.28</v>
+        <v>42599.72</v>
       </c>
       <c r="D86" t="n">
-        <v>948137.02</v>
+        <v>192258.65</v>
       </c>
       <c r="E86" t="n">
-        <v>1451991.47</v>
+        <v>192350.74</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>-7178950.609999999</v>
+        <v>-628161.29</v>
       </c>
       <c r="H86" t="n">
-        <v>-3538950.61</v>
+        <v>3011838.71</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>河北联同医疗器械销售有限公司</t>
+          <t>河北佰汀商贸有限公司</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -72020,28 +72020,28 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>636792.59</v>
+        <v>655363.9399999999</v>
       </c>
       <c r="D87" t="n">
-        <v>498641.77</v>
+        <v>53932.2</v>
       </c>
       <c r="E87" t="n">
-        <v>221726.06</v>
+        <v>417.61</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>-2802218.45</v>
+        <v>532056.99</v>
       </c>
       <c r="H87" t="n">
-        <v>837781.55</v>
+        <v>4172056.99</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>河北天绘少年教育研学科技有限公司</t>
+          <t>石家庄世征科技有限公司</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -72050,28 +72050,28 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>92733.36</v>
+        <v>74484.74000000001</v>
       </c>
       <c r="D88" t="n">
-        <v>197447.31</v>
+        <v>198515.66</v>
       </c>
       <c r="E88" t="n">
-        <v>428205.21</v>
+        <v>85482.48</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>-900336.3799999999</v>
+        <v>-565092.1000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>2739663.62</v>
+        <v>3074907.9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>石家庄靚捷物业服务有限公司</t>
+          <t>河北桥牌体育发展有限公司</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -72080,28 +72080,28 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>24746.01</v>
+        <v>218568.32</v>
       </c>
       <c r="D89" t="n">
-        <v>67046.62</v>
+        <v>112652.29</v>
       </c>
       <c r="E89" t="n">
-        <v>67899.03999999999</v>
+        <v>94107.32000000001</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>372774.6200000001</v>
+        <v>27326.65000000001</v>
       </c>
       <c r="H89" t="n">
-        <v>4012774.62</v>
+        <v>3667326.65</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>石家庄冀凡商贸有限公司</t>
+          <t>华艺博展装饰有限公司</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -72110,28 +72110,28 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>93316.82000000001</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>96801.35000000001</v>
+        <v>202891.45</v>
       </c>
       <c r="E90" t="n">
-        <v>99588.21000000001</v>
+        <v>499951</v>
       </c>
       <c r="F90" t="n">
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>132802.34</v>
+        <v>-1010191.15</v>
       </c>
       <c r="H90" t="n">
-        <v>3772802.34</v>
+        <v>2629808.85</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>河北企合互帮科技发展有限公司</t>
+          <t>河北中天世纪通信技术有限公司</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -72140,28 +72140,28 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2526378.99</v>
+        <v>124900.95</v>
       </c>
       <c r="D91" t="n">
-        <v>959198.3</v>
+        <v>125826.19</v>
       </c>
       <c r="E91" t="n">
-        <v>318626.82</v>
+        <v>472.47</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>-6123014.92</v>
+        <v>28744.19999999992</v>
       </c>
       <c r="H91" t="n">
-        <v>-2483014.92</v>
+        <v>3668744.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>石家庄常宏智能科技有限公司</t>
+          <t>河北企合互帮科技发展有限公司</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -72170,28 +72170,28 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1298182.09</v>
+        <v>2526378.99</v>
       </c>
       <c r="D92" t="n">
-        <v>1656483.67</v>
+        <v>959198.3</v>
       </c>
       <c r="E92" t="n">
-        <v>1696350.79</v>
+        <v>318626.82</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>-12381736.48</v>
+        <v>-6123014.92</v>
       </c>
       <c r="H92" t="n">
-        <v>-8741736.48</v>
+        <v>-2483014.92</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>精晶药业股份有限公司</t>
+          <t>石家庄万岑贸易有限公司</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -72200,28 +72200,28 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2149793.84</v>
+        <v>841758.8199999999</v>
       </c>
       <c r="D93" t="n">
-        <v>2001662.49</v>
+        <v>712595.34</v>
       </c>
       <c r="E93" t="n">
-        <v>2742971.55</v>
+        <v>951735.84</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>-15844608.98</v>
+        <v>-5029903.22</v>
       </c>
       <c r="H93" t="n">
-        <v>-12204608.98</v>
+        <v>-1389903.22</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>石家庄众汇物流有限公司</t>
+          <t>河北蓝哲科技发展有限公司</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -72230,28 +72230,28 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>9500.540000000001</v>
+        <v>63449.67</v>
       </c>
       <c r="D94" t="n">
-        <v>98818.17999999999</v>
+        <v>268728.37</v>
       </c>
       <c r="E94" t="n">
-        <v>22325.79</v>
+        <v>210991.92</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>195946.95</v>
+        <v>-1182090.51</v>
       </c>
       <c r="H94" t="n">
-        <v>3835946.95</v>
+        <v>2457909.49</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>河北蓝哲科技发展有限公司</t>
+          <t>石家庄市科祥建筑装饰工程有限公司</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -72260,28 +72260,28 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>63449.67</v>
+        <v>104917.73</v>
       </c>
       <c r="D95" t="n">
-        <v>268728.37</v>
+        <v>187071.52</v>
       </c>
       <c r="E95" t="n">
-        <v>210991.92</v>
+        <v>345406.2</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>-1182090.51</v>
+        <v>-744906.8399999999</v>
       </c>
       <c r="H95" t="n">
-        <v>2457909.49</v>
+        <v>2895093.16</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>石家庄万岑贸易有限公司</t>
+          <t>河北加贝金融服务外包有限公司</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -72290,28 +72290,28 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>841758.8199999999</v>
+        <v>12216.58</v>
       </c>
       <c r="D96" t="n">
-        <v>712595.34</v>
+        <v>171608.81</v>
       </c>
       <c r="E96" t="n">
-        <v>951735.84</v>
+        <v>168615.35</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>-5029903.22</v>
+        <v>-459877.0199999999</v>
       </c>
       <c r="H96" t="n">
-        <v>-1389903.22</v>
+        <v>3180122.98</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>石家庄硕创商贸有限公司</t>
+          <t>精晶药业股份有限公司</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -72320,28 +72320,28 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>81489.71000000001</v>
+        <v>2149793.84</v>
       </c>
       <c r="D97" t="n">
-        <v>120378.35</v>
+        <v>2001662.49</v>
       </c>
       <c r="E97" t="n">
-        <v>171876.33</v>
+        <v>2742971.55</v>
       </c>
       <c r="F97" t="n">
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>-104524.78</v>
+        <v>-15844608.98</v>
       </c>
       <c r="H97" t="n">
-        <v>3535475.22</v>
+        <v>-12204608.98</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>石家庄轩辰汽车维修设备销售有限公司</t>
+          <t>河北影领市政工程有限公司</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -72350,28 +72350,28 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>84614.13</v>
+        <v>163521.23</v>
       </c>
       <c r="D98" t="n">
-        <v>140166.85</v>
+        <v>255149.59</v>
       </c>
       <c r="E98" t="n">
-        <v>91771.55</v>
+        <v>97316.69</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>-162939.5</v>
+        <v>-973363.8200000001</v>
       </c>
       <c r="H98" t="n">
-        <v>3477060.5</v>
+        <v>2666636.18</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>际华三五零二职业装有限公司</t>
+          <t>河北永明地质工程机械有限公司</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -72380,28 +72380,28 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>12754721.59</v>
+        <v>8852835.34</v>
       </c>
       <c r="D99" t="n">
-        <v>34899562.41</v>
+        <v>1682278.66</v>
       </c>
       <c r="E99" t="n">
-        <v>16120738.61</v>
+        <v>120986.15</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>-259507675.48</v>
+        <v>-10986936.77</v>
       </c>
       <c r="H99" t="n">
-        <v>-255867675.48</v>
+        <v>-7346936.77</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>石家庄市永通企业管理咨询有限公司</t>
+          <t>石家庄氐宿企业管理咨询有限公司桥西分公司</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -72410,28 +72410,28 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2832671.65</v>
+        <v>307170.35</v>
       </c>
       <c r="D100" t="n">
-        <v>3154117.27</v>
+        <v>471163.98</v>
       </c>
       <c r="E100" t="n">
-        <v>5311017.58</v>
+        <v>287874.26</v>
       </c>
       <c r="F100" t="n">
         <v>1</v>
       </c>
       <c r="G100" t="n">
-        <v>-26479838.47</v>
+        <v>-2676022.12</v>
       </c>
       <c r="H100" t="n">
-        <v>-22839838.47</v>
+        <v>963977.8800000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>石家庄远见水泵制造有限公司</t>
+          <t>石家庄众汇物流有限公司</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -72440,28 +72440,28 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>79241.44</v>
+        <v>9500.540000000001</v>
       </c>
       <c r="D101" t="n">
-        <v>50544.82</v>
+        <v>98818.17999999999</v>
       </c>
       <c r="E101" t="n">
-        <v>8542.08</v>
+        <v>22325.79</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>547644.1800000001</v>
+        <v>195946.95</v>
       </c>
       <c r="H101" t="n">
-        <v>4187644.18</v>
+        <v>3835946.95</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>中京建设集团有限公司</t>
+          <t>石家庄普勤停车服务有限公司</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -72470,28 +72470,28 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1281239.06</v>
+        <v>128094.32</v>
       </c>
       <c r="D102" t="n">
-        <v>396668.47</v>
+        <v>263724.38</v>
       </c>
       <c r="E102" t="n">
-        <v>545405.76</v>
+        <v>59176.95</v>
       </c>
       <c r="F102" t="n">
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>-2412085.05</v>
+        <v>-995247.6100000001</v>
       </c>
       <c r="H102" t="n">
-        <v>1227914.95</v>
+        <v>2644752.39</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>河北强盛风电设备有限公司</t>
+          <t>河北恒青电子科技有限公司</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -72500,28 +72500,28 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>849390.05</v>
+        <v>139230.75</v>
       </c>
       <c r="D103" t="n">
-        <v>3102047.68</v>
+        <v>59982.81</v>
       </c>
       <c r="E103" t="n">
-        <v>3102047.68</v>
+        <v>56090.87</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>-23906381.44</v>
+        <v>434029.46</v>
       </c>
       <c r="H103" t="n">
-        <v>-20266381.44</v>
+        <v>4074029.459999999</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>衡橡科技股份有限公司</t>
+          <t>河北益途建筑机械设备租赁有限公司</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -72530,28 +72530,28 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6412592.4</v>
+        <v>552260.1</v>
       </c>
       <c r="D104" t="n">
-        <v>2046810.26</v>
+        <v>246504.9</v>
       </c>
       <c r="E104" t="n">
-        <v>2040232.51</v>
+        <v>230460.01</v>
       </c>
       <c r="F104" t="n">
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>-15457904.33</v>
+        <v>-1045994.31</v>
       </c>
       <c r="H104" t="n">
-        <v>-11817904.33</v>
+        <v>2594005.69</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>石家庄市裕华区淘宝贝高瞻幼儿园</t>
+          <t>河北易昆企业管理咨询有限公司</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -72560,28 +72560,28 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>336817.49</v>
+        <v>392986.85</v>
       </c>
       <c r="D105" t="n">
-        <v>148397.63</v>
+        <v>84533.14</v>
       </c>
       <c r="E105" t="n">
-        <v>264922.27</v>
+        <v>88060.87</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>-393705.68</v>
+        <v>230207.15</v>
       </c>
       <c r="H105" t="n">
-        <v>3246294.32</v>
+        <v>3870207.15</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>欣诚信息技术有限公司</t>
+          <t>河北锅圈食汇商业管理有限公司</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -72590,28 +72590,28 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>961524.5600000001</v>
+        <v>1210852.28</v>
       </c>
       <c r="D106" t="n">
-        <v>940139.49</v>
+        <v>948137.02</v>
       </c>
       <c r="E106" t="n">
-        <v>186877.13</v>
+        <v>1451991.47</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>-5857853.56</v>
+        <v>-7178950.609999999</v>
       </c>
       <c r="H106" t="n">
-        <v>-2217853.56</v>
+        <v>-3538950.61</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>河北影领市政工程有限公司</t>
+          <t>河北联同医疗器械销售有限公司</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -72620,28 +72620,28 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>163521.23</v>
+        <v>636792.59</v>
       </c>
       <c r="D107" t="n">
-        <v>255149.59</v>
+        <v>498641.77</v>
       </c>
       <c r="E107" t="n">
-        <v>97316.69</v>
+        <v>221726.06</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>-973363.8200000001</v>
+        <v>-2802218.45</v>
       </c>
       <c r="H107" t="n">
-        <v>2666636.18</v>
+        <v>837781.55</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>河北加贝金融服务外包有限公司</t>
+          <t>河北天绘少年教育研学科技有限公司</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -72650,28 +72650,28 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>12216.58</v>
+        <v>92733.36</v>
       </c>
       <c r="D108" t="n">
-        <v>171608.81</v>
+        <v>197447.31</v>
       </c>
       <c r="E108" t="n">
-        <v>168615.35</v>
+        <v>428205.21</v>
       </c>
       <c r="F108" t="n">
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>-459877.0199999999</v>
+        <v>-900336.3799999999</v>
       </c>
       <c r="H108" t="n">
-        <v>3180122.98</v>
+        <v>2739663.62</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>河北易昆企业管理咨询有限公司</t>
+          <t>石家庄常宏智能科技有限公司</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -72680,28 +72680,28 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>392986.85</v>
+        <v>1298182.09</v>
       </c>
       <c r="D109" t="n">
-        <v>84533.14</v>
+        <v>1656483.67</v>
       </c>
       <c r="E109" t="n">
-        <v>88060.87</v>
+        <v>1696350.79</v>
       </c>
       <c r="F109" t="n">
         <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>230207.15</v>
+        <v>-12381736.48</v>
       </c>
       <c r="H109" t="n">
-        <v>3870207.15</v>
+        <v>-8741736.48</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>石家庄市科祥建筑装饰工程有限公司</t>
+          <t>石家庄靚捷物业服务有限公司</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -72710,28 +72710,28 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>104917.73</v>
+        <v>24746.01</v>
       </c>
       <c r="D110" t="n">
-        <v>187071.52</v>
+        <v>67046.62</v>
       </c>
       <c r="E110" t="n">
-        <v>345406.2</v>
+        <v>67899.03999999999</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>-744906.8399999999</v>
+        <v>372774.6200000001</v>
       </c>
       <c r="H110" t="n">
-        <v>2895093.16</v>
+        <v>4012774.62</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>石家庄市途祥商贸有限公司</t>
+          <t>石家庄硕创商贸有限公司</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -72740,28 +72740,28 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>267864.94</v>
+        <v>81489.71000000001</v>
       </c>
       <c r="D111" t="n">
-        <v>138634.83</v>
+        <v>120378.35</v>
       </c>
       <c r="E111" t="n">
-        <v>5866.77</v>
+        <v>171876.33</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>-66310.57999999996</v>
+        <v>-104524.78</v>
       </c>
       <c r="H111" t="n">
-        <v>3573689.42</v>
+        <v>3535475.22</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>和龙市万润纺织服装有限公司</t>
+          <t>石家庄轩辰汽车维修设备销售有限公司</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -72770,28 +72770,28 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>206295.89</v>
+        <v>84614.13</v>
       </c>
       <c r="D112" t="n">
-        <v>172058.95</v>
+        <v>140166.85</v>
       </c>
       <c r="E112" t="n">
-        <v>171984.79</v>
+        <v>91771.55</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>-466397.4400000001</v>
+        <v>-162939.5</v>
       </c>
       <c r="H112" t="n">
-        <v>3173602.56</v>
+        <v>3477060.5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>河北石药大药房连锁有限公司</t>
+          <t>河北泽涛建设集团有限公司</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -72800,28 +72800,28 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>15319304.31</v>
+        <v>24280.72</v>
       </c>
       <c r="D113" t="n">
-        <v>12667586.93</v>
+        <v>240471.77</v>
       </c>
       <c r="E113" t="n">
-        <v>9028045.949999999</v>
+        <v>25841.28</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>-96791154.46000001</v>
+        <v>-799143.6699999999</v>
       </c>
       <c r="H113" t="n">
-        <v>-93151154.46000001</v>
+        <v>2840856.330000001</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>益海嘉里（石家庄）食品工业有限公司</t>
+          <t>石家庄冀凡商贸有限公司</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -72830,28 +72830,28 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1110219.59</v>
+        <v>93316.82000000001</v>
       </c>
       <c r="D114" t="n">
-        <v>891207.74</v>
+        <v>96801.35000000001</v>
       </c>
       <c r="E114" t="n">
-        <v>891016.4399999999</v>
+        <v>99588.21000000001</v>
       </c>
       <c r="F114" t="n">
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>-6219470.619999999</v>
+        <v>132802.34</v>
       </c>
       <c r="H114" t="n">
-        <v>-2579470.62</v>
+        <v>3772802.34</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>河北泽涛建设集团有限公司</t>
+          <t>河北博晟工程项目管理有限公司</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -72860,538 +72860,538 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>24280.72</v>
+        <v>171113.75</v>
       </c>
       <c r="D115" t="n">
-        <v>240471.77</v>
+        <v>220640.75</v>
       </c>
       <c r="E115" t="n">
-        <v>25841.28</v>
+        <v>158485.51</v>
       </c>
       <c r="F115" t="n">
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>-799143.6699999999</v>
+        <v>-792970.76</v>
       </c>
       <c r="H115" t="n">
-        <v>2840856.330000001</v>
+        <v>2847029.24</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>解放时代（吉林）新能源科技有限公司</t>
+          <t>欣诚信息技术有限公司</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>9592321.73</v>
+        <v>961524.5600000001</v>
       </c>
       <c r="D116" t="n">
-        <v>8139516.01</v>
+        <v>940139.49</v>
       </c>
       <c r="E116" t="n">
-        <v>13229538.48</v>
+        <v>186877.13</v>
       </c>
       <c r="F116" t="n">
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>-69296150.55</v>
+        <v>-5857853.56</v>
       </c>
       <c r="H116" t="n">
-        <v>-65656150.55</v>
+        <v>-2217853.56</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>河北骏腾汽车服务有限公司</t>
+          <t>河北强盛风电设备有限公司</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>315952.01</v>
+        <v>849390.05</v>
       </c>
       <c r="D117" t="n">
-        <v>240594.53</v>
+        <v>3102047.68</v>
       </c>
       <c r="E117" t="n">
-        <v>109661.97</v>
+        <v>3102047.68</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>-883823.6800000002</v>
+        <v>-23906381.44</v>
       </c>
       <c r="H117" t="n">
-        <v>2756176.32</v>
+        <v>-20266381.44</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>石家庄钢为科技有限公司</t>
+          <t>石家庄磊实建材有限公司</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>16750.63</v>
+        <v>424736.07</v>
       </c>
       <c r="D118" t="n">
-        <v>83293.60000000001</v>
+        <v>508089.89</v>
       </c>
       <c r="E118" t="n">
-        <v>44785.34</v>
+        <v>508089.89</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
       </c>
       <c r="G118" t="n">
-        <v>282159.46</v>
+        <v>-3154719.120000001</v>
       </c>
       <c r="H118" t="n">
-        <v>3922159.46</v>
+        <v>485280.8799999995</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>风华线缆有限公司</t>
+          <t>河北石药大药房连锁有限公司</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>52660.27</v>
+        <v>15319304.31</v>
       </c>
       <c r="D119" t="n">
-        <v>94266.07000000001</v>
+        <v>12667586.93</v>
       </c>
       <c r="E119" t="n">
-        <v>94266.07000000001</v>
+        <v>9028045.949999999</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>155871.4399999999</v>
+        <v>-96791154.46000001</v>
       </c>
       <c r="H119" t="n">
-        <v>3795871.44</v>
+        <v>-93151154.46000001</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>河北升阳律师事务所</t>
+          <t>中京建设集团有限公司</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>314104.14</v>
+        <v>1281239.06</v>
       </c>
       <c r="D120" t="n">
-        <v>328331.42</v>
+        <v>396668.47</v>
       </c>
       <c r="E120" t="n">
-        <v>328331.42</v>
+        <v>545405.76</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>-1716651.36</v>
+        <v>-2412085.05</v>
       </c>
       <c r="H120" t="n">
-        <v>1923348.64</v>
+        <v>1227914.95</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>劲超电线电缆有限公司</t>
+          <t>河北融腾人力资源服务有限公司</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>135807.16</v>
+        <v>451928.11</v>
       </c>
       <c r="D121" t="n">
-        <v>502962.86</v>
+        <v>707815.83</v>
       </c>
       <c r="E121" t="n">
-        <v>502962.86</v>
+        <v>676969.39</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>-3113702.879999999</v>
+        <v>-4721680.199999999</v>
       </c>
       <c r="H121" t="n">
-        <v>526297.1200000005</v>
+        <v>-1081680.199999999</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>石家庄连恩商贸有限公司</t>
+          <t>石家庄远见水泵制造有限公司</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1225851.36</v>
+        <v>79241.44</v>
       </c>
       <c r="D122" t="n">
-        <v>269904.86</v>
+        <v>50544.82</v>
       </c>
       <c r="E122" t="n">
-        <v>26069.34</v>
+        <v>8542.08</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>-1005403.36</v>
+        <v>547644.1800000001</v>
       </c>
       <c r="H122" t="n">
-        <v>2634596.64</v>
+        <v>4187644.18</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>河北金柳化纤有限公司</t>
+          <t>可帮（河北）企业管理咨询有限公司</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>643.25</v>
+        <v>998854.39</v>
       </c>
       <c r="D123" t="n">
-        <v>205757</v>
+        <v>1119307.06</v>
       </c>
       <c r="E123" t="n">
-        <v>205757</v>
+        <v>1597036.97</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>-736056</v>
+        <v>-8522186.390000001</v>
       </c>
       <c r="H123" t="n">
-        <v>2903944</v>
+        <v>-4882186.390000001</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>河北永旭电源有限公司</t>
+          <t>石家庄市途祥商贸有限公司</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>26962775.03</v>
+        <v>267864.94</v>
       </c>
       <c r="D124" t="n">
-        <v>1865462.96</v>
+        <v>138634.83</v>
       </c>
       <c r="E124" t="n">
-        <v>26515.24</v>
+        <v>5866.77</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>-12174755.96</v>
+        <v>-66310.57999999996</v>
       </c>
       <c r="H124" t="n">
-        <v>-8534755.960000001</v>
+        <v>3573689.42</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>石家庄宽迈信息科技有限公司</t>
+          <t>和龙市万润纺织服装有限公司</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>663106.62</v>
+        <v>206295.89</v>
       </c>
       <c r="D125" t="n">
-        <v>437740.83</v>
+        <v>172058.95</v>
       </c>
       <c r="E125" t="n">
-        <v>356727.7</v>
+        <v>171984.79</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>-2510913.51</v>
+        <v>-466397.4400000001</v>
       </c>
       <c r="H125" t="n">
-        <v>1129086.49</v>
+        <v>3173602.56</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>河北玖致安装工程有限公司</t>
+          <t>河北宇腾瑞元科技有限公司</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>132644.48</v>
+        <v>349207.39</v>
       </c>
       <c r="D126" t="n">
-        <v>110381.68</v>
+        <v>242175.49</v>
       </c>
       <c r="E126" t="n">
-        <v>149656.09</v>
+        <v>13852.62</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>-12327.84999999995</v>
+        <v>-799081.05</v>
       </c>
       <c r="H126" t="n">
-        <v>3627672.15</v>
+        <v>2840918.95</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>石家庄彦发金属材料销售有限公司</t>
+          <t>石家庄市永通企业管理咨询有限公司</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>555794.46</v>
+        <v>2832671.65</v>
       </c>
       <c r="D127" t="n">
-        <v>985023.91</v>
+        <v>3154117.27</v>
       </c>
       <c r="E127" t="n">
-        <v>1143558.92</v>
+        <v>5311017.58</v>
       </c>
       <c r="F127" t="n">
         <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>-7128726.29</v>
+        <v>-26479838.47</v>
       </c>
       <c r="H127" t="n">
-        <v>-3488726.29</v>
+        <v>-22839838.47</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>石家庄市海森化工有限公司</t>
+          <t>益海嘉里（石家庄）食品工业有限公司</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>285308.42</v>
+        <v>1110219.59</v>
       </c>
       <c r="D128" t="n">
-        <v>408456.58</v>
+        <v>891207.74</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>891016.4399999999</v>
       </c>
       <c r="F128" t="n">
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>-1949196.06</v>
+        <v>-6219470.619999999</v>
       </c>
       <c r="H128" t="n">
-        <v>1690803.94</v>
+        <v>-2579470.62</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>优唯新材料科技有限公司</t>
+          <t>际华三五零二职业装有限公司</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>234010.14</v>
+        <v>12754721.59</v>
       </c>
       <c r="D129" t="n">
-        <v>169477.92</v>
+        <v>34899562.41</v>
       </c>
       <c r="E129" t="n">
-        <v>171426.11</v>
+        <v>16120738.61</v>
       </c>
       <c r="F129" t="n">
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>-447771.55</v>
+        <v>-259507675.48</v>
       </c>
       <c r="H129" t="n">
-        <v>3192228.45</v>
+        <v>-255867675.48</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>河北维力斯羊绒纺织有限公司</t>
+          <t>嘉兴中玮股权投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>682969.95</v>
+        <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>2615043.63</v>
+        <v>6211304.35</v>
       </c>
       <c r="E130" t="n">
-        <v>9823562.33</v>
+        <v>10000</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>-27218867.74</v>
+        <v>-42579130.45</v>
       </c>
       <c r="H130" t="n">
-        <v>-23578867.74</v>
+        <v>-38939130.45</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>兄弟团国际安保服务有限公司</t>
+          <t>衡橡科技股份有限公司</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>828229.5699999999</v>
+        <v>6412592.4</v>
       </c>
       <c r="D131" t="n">
-        <v>950458.85</v>
+        <v>2046810.26</v>
       </c>
       <c r="E131" t="n">
-        <v>2295.29</v>
+        <v>2040232.51</v>
       </c>
       <c r="F131" t="n">
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>-5745507.24</v>
+        <v>-15457904.33</v>
       </c>
       <c r="H131" t="n">
-        <v>-2105507.24</v>
+        <v>-11817904.33</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>石家庄市百家姓房地产经纪有限公司</t>
+          <t>石家庄市裕华区淘宝贝高瞻幼儿园</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>145775.62</v>
+        <v>336817.49</v>
       </c>
       <c r="D132" t="n">
-        <v>79639.14</v>
+        <v>148397.63</v>
       </c>
       <c r="E132" t="n">
-        <v>5309.61</v>
+        <v>264922.27</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>347216.41</v>
+        <v>-393705.68</v>
       </c>
       <c r="H132" t="n">
-        <v>3987216.410000001</v>
+        <v>3246294.32</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>河北竟达工程技术服务有限公司</t>
+          <t>河北欣康投资有限公司</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -73400,28 +73400,28 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>87920.91</v>
+        <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>110805.95</v>
+        <v>544409.64</v>
       </c>
       <c r="E133" t="n">
-        <v>123602.65</v>
+        <v>834352.49</v>
       </c>
       <c r="F133" t="n">
         <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>10755.70000000001</v>
+        <v>-3735219.970000001</v>
       </c>
       <c r="H133" t="n">
-        <v>3650755.7</v>
+        <v>-95219.97000000044</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>河北欣康投资有限公司</t>
+          <t>河北骏腾汽车服务有限公司</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -73430,22 +73430,22 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>315952.01</v>
       </c>
       <c r="D134" t="n">
-        <v>544409.64</v>
+        <v>240594.53</v>
       </c>
       <c r="E134" t="n">
-        <v>834352.49</v>
+        <v>109661.97</v>
       </c>
       <c r="F134" t="n">
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>-3735219.970000001</v>
+        <v>-883823.6800000002</v>
       </c>
       <c r="H134" t="n">
-        <v>-95219.97000000044</v>
+        <v>2756176.32</v>
       </c>
     </row>
     <row r="135">
@@ -73481,7 +73481,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>石家庄清源泽环保科技有限公司</t>
+          <t>石家庄市海森化工有限公司</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -73490,28 +73490,28 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>245112.73</v>
+        <v>285308.42</v>
       </c>
       <c r="D136" t="n">
-        <v>100695.58</v>
+        <v>408456.58</v>
       </c>
       <c r="E136" t="n">
-        <v>100679.64</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
         <v>1</v>
       </c>
       <c r="G136" t="n">
-        <v>104451.2999999999</v>
+        <v>-1949196.06</v>
       </c>
       <c r="H136" t="n">
-        <v>3744451.3</v>
+        <v>1690803.94</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司</t>
+          <t>宏鑫电缆有限公司</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -73520,28 +73520,28 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>65677123.44</v>
+        <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>156283177.79</v>
+        <v>274138.45</v>
       </c>
       <c r="E137" t="n">
-        <v>133884169.3</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>-1226956413.83</v>
+        <v>-1008969.15</v>
       </c>
       <c r="H137" t="n">
-        <v>-1223316413.83</v>
+        <v>2631030.85</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>河北有朴建筑装饰工程有限公司</t>
+          <t>兄弟团国际安保服务有限公司</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -73550,28 +73550,28 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>75633.73</v>
+        <v>828229.5699999999</v>
       </c>
       <c r="D138" t="n">
-        <v>226168.35</v>
+        <v>950458.85</v>
       </c>
       <c r="E138" t="n">
-        <v>523106.99</v>
+        <v>2295.29</v>
       </c>
       <c r="F138" t="n">
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>-1196285.44</v>
+        <v>-5745507.24</v>
       </c>
       <c r="H138" t="n">
-        <v>2443714.56</v>
+        <v>-2105507.24</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>石家庄乐学乐思培训学校有限公司</t>
+          <t>河北永旭电源有限公司</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -73580,28 +73580,28 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>88850.42</v>
+        <v>26962775.03</v>
       </c>
       <c r="D139" t="n">
-        <v>66693.86</v>
+        <v>1865462.96</v>
       </c>
       <c r="E139" t="n">
-        <v>68011.83</v>
+        <v>26515.24</v>
       </c>
       <c r="F139" t="n">
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>375131.15</v>
+        <v>-12174755.96</v>
       </c>
       <c r="H139" t="n">
-        <v>4015131.149999999</v>
+        <v>-8534755.960000001</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>河北星源密封件集团有限公司</t>
+          <t>石家庄清源泽环保科技有限公司</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -73610,28 +73610,28 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>367599.86</v>
+        <v>245112.73</v>
       </c>
       <c r="D140" t="n">
-        <v>68916.60000000001</v>
+        <v>100695.58</v>
       </c>
       <c r="E140" t="n">
-        <v>44422.78</v>
+        <v>100679.64</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>383161.02</v>
+        <v>104451.2999999999</v>
       </c>
       <c r="H140" t="n">
-        <v>4023161.02</v>
+        <v>3744451.3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>海南北纬十八度科技有限公司</t>
+          <t>河北玖致安装工程有限公司</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -73640,28 +73640,28 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1369732.99</v>
+        <v>132644.48</v>
       </c>
       <c r="D141" t="n">
-        <v>461043.4</v>
+        <v>110381.68</v>
       </c>
       <c r="E141" t="n">
-        <v>451509.3</v>
+        <v>149656.09</v>
       </c>
       <c r="F141" t="n">
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>-2768813.1</v>
+        <v>-12327.84999999995</v>
       </c>
       <c r="H141" t="n">
-        <v>871186.8999999999</v>
+        <v>3627672.15</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>瑞天线缆有限公司</t>
+          <t>河北维力斯羊绒纺织有限公司</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -73670,28 +73670,28 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>682969.95</v>
       </c>
       <c r="D142" t="n">
-        <v>53232.2</v>
+        <v>2615043.63</v>
       </c>
       <c r="E142" t="n">
-        <v>13560.21</v>
+        <v>9823562.33</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>523814.39</v>
+        <v>-27218867.74</v>
       </c>
       <c r="H142" t="n">
-        <v>4163814.39</v>
+        <v>-23578867.74</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>石家庄江建电气安装有限公司</t>
+          <t>石家庄彦发金属材料销售有限公司</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -73700,28 +73700,28 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>174002.91</v>
+        <v>555794.46</v>
       </c>
       <c r="D143" t="n">
-        <v>60146.34</v>
+        <v>985023.91</v>
       </c>
       <c r="E143" t="n">
-        <v>105764.46</v>
+        <v>1143558.92</v>
       </c>
       <c r="F143" t="n">
         <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>383211.16</v>
+        <v>-7128726.29</v>
       </c>
       <c r="H143" t="n">
-        <v>4023211.16</v>
+        <v>-3488726.29</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>石家庄沃尔森贸易有限公司</t>
+          <t>河北有朴建筑装饰工程有限公司</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -73730,28 +73730,28 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1869822.45</v>
+        <v>75633.73</v>
       </c>
       <c r="D144" t="n">
-        <v>1491073.29</v>
+        <v>226168.35</v>
       </c>
       <c r="E144" t="n">
-        <v>873814.1</v>
+        <v>523106.99</v>
       </c>
       <c r="F144" t="n">
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>-10401327.13</v>
+        <v>-1196285.44</v>
       </c>
       <c r="H144" t="n">
-        <v>-6761327.129999999</v>
+        <v>2443714.56</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>河北富迎建材科技有限公司</t>
+          <t>石家庄连恩商贸有限公司</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -73760,28 +73760,28 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>91662.71000000001</v>
+        <v>1225851.36</v>
       </c>
       <c r="D145" t="n">
-        <v>73078.19</v>
+        <v>269904.86</v>
       </c>
       <c r="E145" t="n">
-        <v>52592.24</v>
+        <v>26069.34</v>
       </c>
       <c r="F145" t="n">
         <v>1</v>
       </c>
       <c r="G145" t="n">
-        <v>345860.4300000001</v>
+        <v>-1005403.36</v>
       </c>
       <c r="H145" t="n">
-        <v>3985860.43</v>
+        <v>2634596.64</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>五弘线缆集团有限公司</t>
+          <t>石家庄宽迈信息科技有限公司</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -73790,28 +73790,28 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>226600.69</v>
+        <v>663106.62</v>
       </c>
       <c r="D146" t="n">
-        <v>188051.47</v>
+        <v>437740.83</v>
       </c>
       <c r="E146" t="n">
-        <v>50917.56</v>
+        <v>356727.7</v>
       </c>
       <c r="F146" t="n">
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>-457277.85</v>
+        <v>-2510913.51</v>
       </c>
       <c r="H146" t="n">
-        <v>3182722.15</v>
+        <v>1129086.49</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>围场满族蒙古族自治县塞韵光伏发电有限责任公司</t>
+          <t>石家庄乐学乐思培训学校有限公司</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -73820,28 +73820,28 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>69597.42</v>
+        <v>88850.42</v>
       </c>
       <c r="D147" t="n">
-        <v>272326.64</v>
+        <v>66693.86</v>
       </c>
       <c r="E147" t="n">
-        <v>4093.86</v>
+        <v>68011.83</v>
       </c>
       <c r="F147" t="n">
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>-1000380.34</v>
+        <v>375131.15</v>
       </c>
       <c r="H147" t="n">
-        <v>2639619.66</v>
+        <v>4015131.149999999</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>石家庄舒源装饰工程有限公司</t>
+          <t>优唯新材料科技有限公司</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -73850,28 +73850,28 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>363848.32</v>
+        <v>234010.14</v>
       </c>
       <c r="D148" t="n">
-        <v>170978.48</v>
+        <v>169477.92</v>
       </c>
       <c r="E148" t="n">
-        <v>654543.84</v>
+        <v>171426.11</v>
       </c>
       <c r="F148" t="n">
         <v>1</v>
       </c>
       <c r="G148" t="n">
-        <v>-941393.2000000002</v>
+        <v>-447771.55</v>
       </c>
       <c r="H148" t="n">
-        <v>2698606.8</v>
+        <v>3192228.45</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>石家庄金正物业服务有限公司</t>
+          <t>解放时代（吉林）新能源科技有限公司</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -73880,28 +73880,28 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>17094.56</v>
+        <v>9592321.73</v>
       </c>
       <c r="D149" t="n">
-        <v>86583.36</v>
+        <v>8139516.01</v>
       </c>
       <c r="E149" t="n">
-        <v>38971.88</v>
+        <v>13229538.48</v>
       </c>
       <c r="F149" t="n">
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>264944.6</v>
+        <v>-69296150.55</v>
       </c>
       <c r="H149" t="n">
-        <v>3904944.6</v>
+        <v>-65656150.55</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>西康软件有限责任公司</t>
+          <t>五弘线缆集团有限公司</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -73910,28 +73910,28 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>491258.64</v>
+        <v>226600.69</v>
       </c>
       <c r="D150" t="n">
-        <v>207147.92</v>
+        <v>188051.47</v>
       </c>
       <c r="E150" t="n">
-        <v>389722.85</v>
+        <v>50917.56</v>
       </c>
       <c r="F150" t="n">
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>-929758.29</v>
+        <v>-457277.85</v>
       </c>
       <c r="H150" t="n">
-        <v>2710241.71</v>
+        <v>3182722.15</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>石家庄市金世纪电缆有限公司</t>
+          <t>石家庄市百家姓房地产经纪有限公司</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -73940,28 +73940,28 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>223597.32</v>
+        <v>145775.62</v>
       </c>
       <c r="D151" t="n">
-        <v>106641.37</v>
+        <v>79639.14</v>
       </c>
       <c r="E151" t="n">
-        <v>106820.87</v>
+        <v>5309.61</v>
       </c>
       <c r="F151" t="n">
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>56689.54000000007</v>
+        <v>347216.41</v>
       </c>
       <c r="H151" t="n">
-        <v>3696689.54</v>
+        <v>3987216.410000001</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>河北世翔密封件有限公司</t>
+          <t>康保县省直保供基地有限公司</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -73970,28 +73970,28 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>311433.26</v>
+        <v>57861.69</v>
       </c>
       <c r="D152" t="n">
-        <v>396004.32</v>
+        <v>109867.93</v>
       </c>
       <c r="E152" t="n">
-        <v>30682.98</v>
+        <v>109867.93</v>
       </c>
       <c r="F152" t="n">
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>-1892713.22</v>
+        <v>31056.56000000006</v>
       </c>
       <c r="H152" t="n">
-        <v>1747286.78</v>
+        <v>3671056.56</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>河北绿诺食品有限公司</t>
+          <t>河北竟达工程技术服务有限公司</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -74000,28 +74000,28 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>163268.24</v>
+        <v>87920.91</v>
       </c>
       <c r="D153" t="n">
-        <v>1123362.75</v>
+        <v>110805.95</v>
       </c>
       <c r="E153" t="n">
-        <v>257265.7</v>
+        <v>123602.65</v>
       </c>
       <c r="F153" t="n">
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>-7210804.95</v>
+        <v>10755.70000000001</v>
       </c>
       <c r="H153" t="n">
-        <v>-3570804.95</v>
+        <v>3650755.7</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>河北华曙新能源汽车科技有限公司</t>
+          <t>石家庄舒源装饰工程有限公司</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -74030,28 +74030,28 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>194439.82</v>
+        <v>363848.32</v>
       </c>
       <c r="D154" t="n">
-        <v>98861</v>
+        <v>170978.48</v>
       </c>
       <c r="E154" t="n">
-        <v>41781.81</v>
+        <v>654543.84</v>
       </c>
       <c r="F154" t="n">
         <v>1</v>
       </c>
       <c r="G154" t="n">
-        <v>176191.19</v>
+        <v>-941393.2000000002</v>
       </c>
       <c r="H154" t="n">
-        <v>3816191.19</v>
+        <v>2698606.8</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>康保县省直保供基地有限公司</t>
+          <t>围场满族蒙古族自治县塞韵光伏发电有限责任公司</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -74060,28 +74060,28 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>57861.69</v>
+        <v>69597.42</v>
       </c>
       <c r="D155" t="n">
-        <v>109867.93</v>
+        <v>272326.64</v>
       </c>
       <c r="E155" t="n">
-        <v>109867.93</v>
+        <v>4093.86</v>
       </c>
       <c r="F155" t="n">
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>31056.56000000006</v>
+        <v>-1000380.34</v>
       </c>
       <c r="H155" t="n">
-        <v>3671056.56</v>
+        <v>2639619.66</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>河北亚诚科技有限公司</t>
+          <t>河北绿诺食品有限公司</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -74090,652 +74090,652 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2893146.15</v>
+        <v>163268.24</v>
       </c>
       <c r="D156" t="n">
-        <v>2661664.94</v>
+        <v>1123362.75</v>
       </c>
       <c r="E156" t="n">
-        <v>2616835.33</v>
+        <v>257265.7</v>
       </c>
       <c r="F156" t="n">
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>-20338489.91</v>
+        <v>-7210804.95</v>
       </c>
       <c r="H156" t="n">
-        <v>-16698489.91</v>
+        <v>-3570804.95</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>河北冀石云建设工程有限公司</t>
+          <t>风华线缆有限公司</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>邸平花</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>472015.75</v>
+        <v>52660.27</v>
       </c>
       <c r="D157" t="n">
-        <v>443320.09</v>
+        <v>94266.07000000001</v>
       </c>
       <c r="E157" t="n">
-        <v>578658.03</v>
+        <v>94266.07000000001</v>
       </c>
       <c r="F157" t="n">
         <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>-2771898.66</v>
+        <v>155871.4399999999</v>
       </c>
       <c r="H157" t="n">
-        <v>868101.3399999999</v>
+        <v>3795871.44</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>河北洱涵企业管理有限公司</t>
+          <t>河北金柳化纤有限公司</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>邸平花</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>228620.27</v>
+        <v>643.25</v>
       </c>
       <c r="D158" t="n">
-        <v>135289</v>
+        <v>205757</v>
       </c>
       <c r="E158" t="n">
-        <v>111765.08</v>
+        <v>205757</v>
       </c>
       <c r="F158" t="n">
         <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>-148788.08</v>
+        <v>-736056</v>
       </c>
       <c r="H158" t="n">
-        <v>3491211.92</v>
+        <v>2903944</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>河北恒丰华怡商务服务有限责任公司恒丰大酒店</t>
+          <t>河北升阳律师事务所</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>邸平花</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>321333.12</v>
+        <v>314104.14</v>
       </c>
       <c r="D159" t="n">
-        <v>301457.19</v>
+        <v>328331.42</v>
       </c>
       <c r="E159" t="n">
-        <v>352672.99</v>
+        <v>328331.42</v>
       </c>
       <c r="F159" t="n">
         <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>-1552873.32</v>
+        <v>-1716651.36</v>
       </c>
       <c r="H159" t="n">
-        <v>2087126.68</v>
+        <v>1923348.64</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>石家庄横琴企业管理有限公司</t>
+          <t>劲超电线电缆有限公司</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>189997.22</v>
+        <v>135807.16</v>
       </c>
       <c r="D160" t="n">
-        <v>320236.48</v>
+        <v>502962.86</v>
       </c>
       <c r="E160" t="n">
-        <v>294184.74</v>
+        <v>502962.86</v>
       </c>
       <c r="F160" t="n">
         <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>-1625840.1</v>
+        <v>-3113702.879999999</v>
       </c>
       <c r="H160" t="n">
-        <v>2014159.9</v>
+        <v>526297.1200000005</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>河北春鼎物业管理有限公司</t>
+          <t>海南北纬十八度科技有限公司</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>36868.67</v>
+        <v>1369732.99</v>
       </c>
       <c r="D161" t="n">
-        <v>52439.35</v>
+        <v>461043.4</v>
       </c>
       <c r="E161" t="n">
-        <v>53950.3</v>
+        <v>451509.3</v>
       </c>
       <c r="F161" t="n">
         <v>1</v>
       </c>
       <c r="G161" t="n">
-        <v>488974.2500000001</v>
+        <v>-2768813.1</v>
       </c>
       <c r="H161" t="n">
-        <v>4128974.25</v>
+        <v>871186.8999999999</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>秦皇岛发源建材装饰工程有限公司</t>
+          <t>石家庄江建电气安装有限公司</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>18933.13</v>
+        <v>174002.91</v>
       </c>
       <c r="D162" t="n">
-        <v>51202.39</v>
+        <v>60146.34</v>
       </c>
       <c r="E162" t="n">
-        <v>11028.2</v>
+        <v>105764.46</v>
       </c>
       <c r="F162" t="n">
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>540555.0700000001</v>
+        <v>383211.16</v>
       </c>
       <c r="H162" t="n">
-        <v>4180555.07</v>
+        <v>4023211.16</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>河北益安诚人力资源服务有限公司</t>
+          <t>石家庄沃尔森贸易有限公司</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2387702.52</v>
+        <v>1869822.45</v>
       </c>
       <c r="D163" t="n">
-        <v>2380909.83</v>
+        <v>1491073.29</v>
       </c>
       <c r="E163" t="n">
-        <v>2263042.01</v>
+        <v>873814.1</v>
       </c>
       <c r="F163" t="n">
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>-18019410.82</v>
+        <v>-10401327.13</v>
       </c>
       <c r="H163" t="n">
-        <v>-14379410.82</v>
+        <v>-6761327.129999999</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>石家庄铭派机电有限公司</t>
+          <t>河北华曙新能源汽车科技有限公司</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>855166.83</v>
+        <v>194439.82</v>
       </c>
       <c r="D164" t="n">
-        <v>1055659.03</v>
+        <v>98861</v>
       </c>
       <c r="E164" t="n">
-        <v>1326606.98</v>
+        <v>41781.81</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>-7806220.190000001</v>
+        <v>176191.19</v>
       </c>
       <c r="H164" t="n">
-        <v>-4166220.190000001</v>
+        <v>3816191.19</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>河北文通国际贸易有限公司</t>
+          <t>石家庄金正物业服务有限公司</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>5172907.01</v>
+        <v>17094.56</v>
       </c>
       <c r="D165" t="n">
-        <v>5190279.6</v>
+        <v>86583.36</v>
       </c>
       <c r="E165" t="n">
-        <v>5190279.6</v>
+        <v>38971.88</v>
       </c>
       <c r="F165" t="n">
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>-40612236.8</v>
+        <v>264944.6</v>
       </c>
       <c r="H165" t="n">
-        <v>-36972236.8</v>
+        <v>3904944.6</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>宏鑫电缆有限公司</t>
+          <t>河北世翔密封件有限公司</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>311433.26</v>
       </c>
       <c r="D166" t="n">
-        <v>274138.45</v>
+        <v>396004.32</v>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>30682.98</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>-1008969.15</v>
+        <v>-1892713.22</v>
       </c>
       <c r="H166" t="n">
-        <v>2631030.85</v>
+        <v>1747286.78</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>石家庄企合科技有限公司</t>
+          <t>河北星源密封件集团有限公司</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>211284.44</v>
+        <v>367599.86</v>
       </c>
       <c r="D167" t="n">
-        <v>316241.34</v>
+        <v>68916.60000000001</v>
       </c>
       <c r="E167" t="n">
-        <v>369312.53</v>
+        <v>44422.78</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>-1673001.91</v>
+        <v>383161.02</v>
       </c>
       <c r="H167" t="n">
-        <v>1966998.09</v>
+        <v>4023161.02</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>合一智慧物流服务（河北）有限公司</t>
+          <t>瑞天线缆有限公司</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>103827.62</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>884737.75</v>
+        <v>53232.2</v>
       </c>
       <c r="E168" t="n">
-        <v>1959463.61</v>
+        <v>13560.21</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>-7242627.86</v>
+        <v>523814.39</v>
       </c>
       <c r="H168" t="n">
-        <v>-3602627.86</v>
+        <v>4163814.39</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>河北梵州信息技术有限公司</t>
+          <t>河北富迎建材科技有限公司</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>344989.03</v>
+        <v>91662.71000000001</v>
       </c>
       <c r="D169" t="n">
-        <v>283824.22</v>
+        <v>73078.19</v>
       </c>
       <c r="E169" t="n">
-        <v>279463.96</v>
+        <v>52592.24</v>
       </c>
       <c r="F169" t="n">
         <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>-1356233.5</v>
+        <v>345860.4300000001</v>
       </c>
       <c r="H169" t="n">
-        <v>2283766.5</v>
+        <v>3985860.43</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>石家庄市陆升水处理设备有限公司</t>
+          <t>西康软件有限责任公司</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>128169.9</v>
+        <v>491258.64</v>
       </c>
       <c r="D170" t="n">
-        <v>82160.38</v>
+        <v>207147.92</v>
       </c>
       <c r="E170" t="n">
-        <v>5275.41</v>
+        <v>389722.85</v>
       </c>
       <c r="F170" t="n">
         <v>1</v>
       </c>
       <c r="G170" t="n">
-        <v>329601.93</v>
+        <v>-929758.29</v>
       </c>
       <c r="H170" t="n">
-        <v>3969601.93</v>
+        <v>2710241.71</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>石家庄健牛科技有限公司</t>
+          <t>河北亚诚科技有限公司</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>124580.27</v>
+        <v>2893146.15</v>
       </c>
       <c r="D171" t="n">
-        <v>169460.46</v>
+        <v>2661664.94</v>
       </c>
       <c r="E171" t="n">
-        <v>105541.79</v>
+        <v>2616835.33</v>
       </c>
       <c r="F171" t="n">
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>-381765.0099999999</v>
+        <v>-20338489.91</v>
       </c>
       <c r="H171" t="n">
-        <v>3258234.99</v>
+        <v>-16698489.91</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>河北图佳智联科技有限公司</t>
+          <t>石家庄钢为科技有限公司</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>317501.33</v>
+        <v>16750.63</v>
       </c>
       <c r="D172" t="n">
-        <v>269454.77</v>
+        <v>83293.60000000001</v>
       </c>
       <c r="E172" t="n">
-        <v>265467.29</v>
+        <v>44785.34</v>
       </c>
       <c r="F172" t="n">
         <v>1</v>
       </c>
       <c r="G172" t="n">
-        <v>-1241650.68</v>
+        <v>282159.46</v>
       </c>
       <c r="H172" t="n">
-        <v>2398349.32</v>
+        <v>3922159.46</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>河北益丰生物医药有限公司</t>
+          <t>解放时代新能源科技有限公司</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>543809.28</v>
+        <v>65677123.44</v>
       </c>
       <c r="D173" t="n">
-        <v>284463.57</v>
+        <v>156283177.79</v>
       </c>
       <c r="E173" t="n">
-        <v>246166.78</v>
+        <v>133884169.3</v>
       </c>
       <c r="F173" t="n">
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>-1327411.77</v>
+        <v>-1226956413.83</v>
       </c>
       <c r="H173" t="n">
-        <v>2312588.23</v>
+        <v>-1223316413.83</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>河北康卫仕医疗科技有限公司</t>
+          <t>石家庄市金世纪电缆有限公司</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>123958.77</v>
+        <v>223597.32</v>
       </c>
       <c r="D174" t="n">
-        <v>155374.76</v>
+        <v>106641.37</v>
       </c>
       <c r="E174" t="n">
-        <v>74026.00999999999</v>
+        <v>106820.87</v>
       </c>
       <c r="F174" t="n">
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>-251649.3300000001</v>
+        <v>56689.54000000007</v>
       </c>
       <c r="H174" t="n">
-        <v>3388350.67</v>
+        <v>3696689.54</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>河北博斯特展览服务有限公司</t>
+          <t>河北洱涵企业管理有限公司</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>邸平花</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>273867.56</v>
+        <v>228620.27</v>
       </c>
       <c r="D175" t="n">
-        <v>73759.55</v>
+        <v>135289</v>
       </c>
       <c r="E175" t="n">
-        <v>201805.43</v>
+        <v>111765.08</v>
       </c>
       <c r="F175" t="n">
         <v>1</v>
       </c>
       <c r="G175" t="n">
-        <v>191877.72</v>
+        <v>-148788.08</v>
       </c>
       <c r="H175" t="n">
-        <v>3831877.72</v>
+        <v>3491211.92</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>河北仁恒工程管理服务有限公司</t>
+          <t>河北恒丰华怡商务服务有限责任公司恒丰大酒店</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>邸平花</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>172758.08</v>
+        <v>321333.12</v>
       </c>
       <c r="D176" t="n">
-        <v>82215.39999999999</v>
+        <v>301457.19</v>
       </c>
       <c r="E176" t="n">
-        <v>82952.86</v>
+        <v>352672.99</v>
       </c>
       <c r="F176" t="n">
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>251539.34</v>
+        <v>-1552873.32</v>
       </c>
       <c r="H176" t="n">
-        <v>3891539.34</v>
+        <v>2087126.68</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>河北文轩贸易有限公司</t>
+          <t>河北冀石云建设工程有限公司</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>邸平花</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>620898.98</v>
+        <v>472015.75</v>
       </c>
       <c r="D177" t="n">
-        <v>4282108.85</v>
+        <v>443320.09</v>
       </c>
       <c r="E177" t="n">
-        <v>93739.86</v>
+        <v>578658.03</v>
       </c>
       <c r="F177" t="n">
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>-29158501.81</v>
+        <v>-2771898.66</v>
       </c>
       <c r="H177" t="n">
-        <v>-25518501.81</v>
+        <v>868101.3399999999</v>
       </c>
     </row>
   </sheetData>
@@ -74857,7 +74857,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>石家庄敏成建筑信息咨询有限公司</t>
+          <t>石家庄赛丝科技有限公司</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -74866,28 +74866,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1842328.5</v>
+        <v>562360.88</v>
       </c>
       <c r="D4" t="n">
-        <v>2448805.38</v>
+        <v>499299.47</v>
       </c>
       <c r="E4" t="n">
-        <v>54167.61</v>
+        <v>412120.9</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>-16285805.27</v>
+        <v>-2997217.19</v>
       </c>
       <c r="H4" t="n">
-        <v>-12645805.27</v>
+        <v>642782.8100000002</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>石家庄居然丽居装饰材料有限公司</t>
+          <t>石家庄敏成建筑信息咨询有限公司</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -74896,28 +74896,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4543396.24</v>
+        <v>1842328.5</v>
       </c>
       <c r="D5" t="n">
-        <v>3892614.36</v>
+        <v>2448805.38</v>
       </c>
       <c r="E5" t="n">
-        <v>2931031.81</v>
+        <v>54167.61</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>-29269332.33</v>
+        <v>-16285805.27</v>
       </c>
       <c r="H5" t="n">
-        <v>-25629332.33</v>
+        <v>-12645805.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>石家庄赛丝科技有限公司</t>
+          <t>石家庄居然丽居装饰材料有限公司</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -74926,28 +74926,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>562360.88</v>
+        <v>4543396.24</v>
       </c>
       <c r="D6" t="n">
-        <v>499299.47</v>
+        <v>3892614.36</v>
       </c>
       <c r="E6" t="n">
-        <v>412120.9</v>
+        <v>2931031.81</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-2997217.19</v>
+        <v>-29269332.33</v>
       </c>
       <c r="H6" t="n">
-        <v>642782.8100000002</v>
+        <v>-25629332.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司成都分公司</t>
+          <t>河北钢铁产业转型升级母基金（有限合伙）</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -74956,22 +74956,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>322920.74</v>
+        <v>4519727.98</v>
       </c>
       <c r="D7" t="n">
-        <v>1183251.82</v>
+        <v>4527721.97</v>
       </c>
       <c r="E7" t="n">
-        <v>1146833</v>
+        <v>4527721.97</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>-8519595.74</v>
+        <v>-35311775.76</v>
       </c>
       <c r="H7" t="n">
-        <v>-4879595.74</v>
+        <v>-31671775.76</v>
       </c>
     </row>
     <row r="8">
@@ -75037,7 +75037,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>西藏汇科华药业有限公司</t>
+          <t>河北益安诚人力资源服务有限公司</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -75046,28 +75046,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13739639.99</v>
+        <v>2387702.52</v>
       </c>
       <c r="D10" t="n">
-        <v>17339236.62</v>
+        <v>2380909.83</v>
       </c>
       <c r="E10" t="n">
-        <v>15487720.18</v>
+        <v>2263042.01</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>-135952376.52</v>
+        <v>-18019410.82</v>
       </c>
       <c r="H10" t="n">
-        <v>-132312376.52</v>
+        <v>-14379410.82</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司哈密分公司</t>
+          <t>西藏汇科华药业有限公司</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -75076,28 +75076,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25021.59</v>
+        <v>13739639.99</v>
       </c>
       <c r="D11" t="n">
-        <v>650761.96</v>
+        <v>17339236.62</v>
       </c>
       <c r="E11" t="n">
-        <v>209979</v>
+        <v>15487720.18</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>-3855312.72</v>
+        <v>-135952376.52</v>
       </c>
       <c r="H11" t="n">
-        <v>-215312.7199999996</v>
+        <v>-132312376.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司厦门分公司</t>
+          <t>合一智慧物流服务（河北）有限公司</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -75106,22 +75106,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>377969.83</v>
+        <v>103827.62</v>
       </c>
       <c r="D12" t="n">
-        <v>1073757.95</v>
+        <v>884737.75</v>
       </c>
       <c r="E12" t="n">
-        <v>637326.78</v>
+        <v>1959463.61</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>-7243632.430000001</v>
+        <v>-7242627.86</v>
       </c>
       <c r="H12" t="n">
-        <v>-3603632.43</v>
+        <v>-3602627.86</v>
       </c>
     </row>
     <row r="13">
@@ -75157,7 +75157,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>河北钢铁产业转型升级母基金（有限合伙）</t>
+          <t>石家庄市申东商贸有限公司</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -75166,28 +75166,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4519727.98</v>
+        <v>537938.5</v>
       </c>
       <c r="D14" t="n">
-        <v>4527721.97</v>
+        <v>545970.4399999999</v>
       </c>
       <c r="E14" t="n">
-        <v>4527721.97</v>
+        <v>505762.15</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>-35311775.76</v>
+        <v>-3417555.23</v>
       </c>
       <c r="H14" t="n">
-        <v>-31671775.76</v>
+        <v>222444.7700000003</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>河北产投基石氢能产业投资基金合伙企业（有限合伙）</t>
+          <t>廊坊隆冀达金属零部件有限公司</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -75196,22 +75196,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6992752.8</v>
+        <v>652679.54</v>
       </c>
       <c r="D15" t="n">
-        <v>4945344.22</v>
+        <v>6930266.93</v>
       </c>
       <c r="E15" t="n">
-        <v>4945344.22</v>
+        <v>9091788.08</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>-38652753.76</v>
+        <v>-56693656.59</v>
       </c>
       <c r="H15" t="n">
-        <v>-35012753.76</v>
+        <v>-53053656.59</v>
       </c>
     </row>
     <row r="16">
@@ -75247,7 +75247,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司湖州分公司</t>
+          <t>解放时代新能源科技有限公司哈密分公司</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -75256,28 +75256,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>644284.63</v>
+        <v>25021.59</v>
       </c>
       <c r="D17" t="n">
-        <v>1391105.26</v>
+        <v>650761.96</v>
       </c>
       <c r="E17" t="n">
-        <v>1806563</v>
+        <v>209979</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>-10634299.82</v>
+        <v>-3855312.72</v>
       </c>
       <c r="H17" t="n">
-        <v>-6994299.82</v>
+        <v>-215312.7199999996</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>廊坊隆冀达金属零部件有限公司</t>
+          <t>河北产投基石氢能产业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -75286,28 +75286,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>652679.54</v>
+        <v>6992752.8</v>
       </c>
       <c r="D18" t="n">
-        <v>6930266.93</v>
+        <v>4945344.22</v>
       </c>
       <c r="E18" t="n">
-        <v>9091788.08</v>
+        <v>4945344.22</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>-56693656.59</v>
+        <v>-38652753.76</v>
       </c>
       <c r="H18" t="n">
-        <v>-53053656.59</v>
+        <v>-35012753.76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>石家庄市申东商贸有限公司</t>
+          <t>石家庄铭派机电有限公司</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -75316,178 +75316,178 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>537938.5</v>
+        <v>855166.83</v>
       </c>
       <c r="D19" t="n">
-        <v>545970.4399999999</v>
+        <v>1055659.03</v>
       </c>
       <c r="E19" t="n">
-        <v>505762.15</v>
+        <v>1326606.98</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>-3417555.23</v>
+        <v>-7806220.190000001</v>
       </c>
       <c r="H19" t="n">
-        <v>222444.7700000003</v>
+        <v>-4166220.190000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>可帮（河北）企业管理咨询有限公司</t>
+          <t>解放时代新能源科技有限公司成都分公司</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>998854.39</v>
+        <v>322920.74</v>
       </c>
       <c r="D20" t="n">
-        <v>1119307.06</v>
+        <v>1183251.82</v>
       </c>
       <c r="E20" t="n">
-        <v>1597036.97</v>
+        <v>1146833</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>-8522186.390000001</v>
+        <v>-8519595.74</v>
       </c>
       <c r="H20" t="n">
-        <v>-4882186.390000001</v>
+        <v>-4879595.74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>河北石药大药房连锁有限公司</t>
+          <t>解放时代新能源科技有限公司厦门分公司</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15319304.31</v>
+        <v>377969.83</v>
       </c>
       <c r="D21" t="n">
-        <v>12667586.93</v>
+        <v>1073757.95</v>
       </c>
       <c r="E21" t="n">
-        <v>9028045.949999999</v>
+        <v>637326.78</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>-96791154.46000001</v>
+        <v>-7243632.430000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-93151154.46000001</v>
+        <v>-3603632.43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>河北衡湖创业投资基金合伙企业（有限合伙）</t>
+          <t>河北文通国际贸易有限公司</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>5172907.01</v>
       </c>
       <c r="D22" t="n">
-        <v>34556376.81</v>
+        <v>5190279.6</v>
       </c>
       <c r="E22" t="n">
-        <v>80800000</v>
+        <v>5190279.6</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>-321784637.67</v>
+        <v>-40612236.8</v>
       </c>
       <c r="H22" t="n">
-        <v>-318144637.67</v>
+        <v>-36972236.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>益海嘉里（石家庄）食品工业有限公司</t>
+          <t>河北文轩贸易有限公司</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1110219.59</v>
+        <v>620898.98</v>
       </c>
       <c r="D23" t="n">
-        <v>891207.74</v>
+        <v>4282108.85</v>
       </c>
       <c r="E23" t="n">
-        <v>891016.4399999999</v>
+        <v>93739.86</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>-6219470.619999999</v>
+        <v>-29158501.81</v>
       </c>
       <c r="H23" t="n">
-        <v>-2579470.62</v>
+        <v>-25518501.81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>石家庄尊唯体育科技有限公司</t>
+          <t>解放时代新能源科技有限公司湖州分公司</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>308627.62</v>
+        <v>644284.63</v>
       </c>
       <c r="D24" t="n">
-        <v>478745.72</v>
+        <v>1391105.26</v>
       </c>
       <c r="E24" t="n">
-        <v>290383.12</v>
+        <v>1806563</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>-2731603.16</v>
+        <v>-10634299.82</v>
       </c>
       <c r="H24" t="n">
-        <v>908396.8400000002</v>
+        <v>-6994299.82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>河北融腾人力资源服务有限公司</t>
+          <t>中义诚河北会计师事务所（普通合伙）</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -75496,28 +75496,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>451928.11</v>
+        <v>684020.15</v>
       </c>
       <c r="D25" t="n">
-        <v>707815.83</v>
+        <v>1311808.25</v>
       </c>
       <c r="E25" t="n">
-        <v>676969.39</v>
+        <v>1311808.25</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>-4721680.199999999</v>
+        <v>-9584466</v>
       </c>
       <c r="H25" t="n">
-        <v>-1081680.199999999</v>
+        <v>-5944466</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>中义诚河北会计师事务所（普通合伙）</t>
+          <t>益海嘉里（石家庄）食品工业有限公司</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -75526,28 +75526,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>684020.15</v>
+        <v>1110219.59</v>
       </c>
       <c r="D26" t="n">
-        <v>1311808.25</v>
+        <v>891207.74</v>
       </c>
       <c r="E26" t="n">
-        <v>1311808.25</v>
+        <v>891016.4399999999</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>-9584466</v>
+        <v>-6219470.619999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-5944466</v>
+        <v>-2579470.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>河北溯瞬信息科技有限公司</t>
+          <t>河北融腾人力资源服务有限公司</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -75556,28 +75556,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>85475.78</v>
+        <v>451928.11</v>
       </c>
       <c r="D27" t="n">
-        <v>1423332.14</v>
+        <v>707815.83</v>
       </c>
       <c r="E27" t="n">
-        <v>100317.94</v>
+        <v>676969.39</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>-9153642.92</v>
+        <v>-4721680.199999999</v>
       </c>
       <c r="H27" t="n">
-        <v>-5513642.92</v>
+        <v>-1081680.199999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>石家庄磊实建材有限公司</t>
+          <t>河北溯瞬信息科技有限公司</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -75586,28 +75586,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>424736.07</v>
+        <v>85475.78</v>
       </c>
       <c r="D28" t="n">
-        <v>508089.89</v>
+        <v>1423332.14</v>
       </c>
       <c r="E28" t="n">
-        <v>508089.89</v>
+        <v>100317.94</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>-3154719.120000001</v>
+        <v>-9153642.92</v>
       </c>
       <c r="H28" t="n">
-        <v>485280.8799999995</v>
+        <v>-5513642.92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>精晶药业股份有限公司</t>
+          <t>石家庄磊实建材有限公司</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -75616,28 +75616,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2149793.84</v>
+        <v>424736.07</v>
       </c>
       <c r="D29" t="n">
-        <v>2001662.49</v>
+        <v>508089.89</v>
       </c>
       <c r="E29" t="n">
-        <v>2742971.55</v>
+        <v>508089.89</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>-15844608.98</v>
+        <v>-3154719.120000001</v>
       </c>
       <c r="H29" t="n">
-        <v>-12204608.98</v>
+        <v>485280.8799999995</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>嘉兴中玮股权投资合伙企业(有限合伙)</t>
+          <t>可帮（河北）企业管理咨询有限公司</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -75646,28 +75646,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>998854.39</v>
       </c>
       <c r="D30" t="n">
-        <v>6211304.35</v>
+        <v>1119307.06</v>
       </c>
       <c r="E30" t="n">
-        <v>10000</v>
+        <v>1597036.97</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>-42579130.45</v>
+        <v>-8522186.390000001</v>
       </c>
       <c r="H30" t="n">
-        <v>-38939130.45</v>
+        <v>-4882186.390000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>石家庄氐宿企业管理咨询有限公司桥西分公司</t>
+          <t>石家庄尊唯体育科技有限公司</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -75676,28 +75676,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>307170.35</v>
+        <v>308627.62</v>
       </c>
       <c r="D31" t="n">
-        <v>471163.98</v>
+        <v>478745.72</v>
       </c>
       <c r="E31" t="n">
-        <v>287874.26</v>
+        <v>290383.12</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>-2676022.12</v>
+        <v>-2731603.16</v>
       </c>
       <c r="H31" t="n">
-        <v>963977.8800000001</v>
+        <v>908396.8400000002</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>欣诚信息技术有限公司</t>
+          <t>河北石药大药房连锁有限公司</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -75706,28 +75706,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>961524.5600000001</v>
+        <v>15319304.31</v>
       </c>
       <c r="D32" t="n">
-        <v>940139.49</v>
+        <v>12667586.93</v>
       </c>
       <c r="E32" t="n">
-        <v>186877.13</v>
+        <v>9028045.949999999</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>-5857853.56</v>
+        <v>-96791154.46000001</v>
       </c>
       <c r="H32" t="n">
-        <v>-2217853.56</v>
+        <v>-93151154.46000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>石家庄市永通企业管理咨询有限公司</t>
+          <t>嘉兴中玮股权投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -75736,28 +75736,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2832671.65</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>3154117.27</v>
+        <v>6211304.35</v>
       </c>
       <c r="E33" t="n">
-        <v>5311017.58</v>
+        <v>10000</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>-26479838.47</v>
+        <v>-42579130.45</v>
       </c>
       <c r="H33" t="n">
-        <v>-22839838.47</v>
+        <v>-38939130.45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>际华三五零二职业装有限公司</t>
+          <t>河北衡湖创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -75766,28 +75766,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>12754721.59</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>34899562.41</v>
+        <v>34556376.81</v>
       </c>
       <c r="E34" t="n">
-        <v>16120738.61</v>
+        <v>80800000</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>-259507675.48</v>
+        <v>-321784637.67</v>
       </c>
       <c r="H34" t="n">
-        <v>-255867675.48</v>
+        <v>-318144637.67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>河北永明地质工程机械有限公司</t>
+          <t>石家庄万岑贸易有限公司</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -75796,28 +75796,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8852835.34</v>
+        <v>841758.8199999999</v>
       </c>
       <c r="D35" t="n">
-        <v>1682278.66</v>
+        <v>712595.34</v>
       </c>
       <c r="E35" t="n">
-        <v>120986.15</v>
+        <v>951735.84</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>-10986936.77</v>
+        <v>-5029903.22</v>
       </c>
       <c r="H35" t="n">
-        <v>-7346936.77</v>
+        <v>-1389903.22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>衡橡科技股份有限公司</t>
+          <t>石家庄常宏智能科技有限公司</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -75826,28 +75826,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6412592.4</v>
+        <v>1298182.09</v>
       </c>
       <c r="D36" t="n">
-        <v>2046810.26</v>
+        <v>1656483.67</v>
       </c>
       <c r="E36" t="n">
-        <v>2040232.51</v>
+        <v>1696350.79</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>-15457904.33</v>
+        <v>-12381736.48</v>
       </c>
       <c r="H36" t="n">
-        <v>-11817904.33</v>
+        <v>-8741736.48</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>石家庄万岑贸易有限公司</t>
+          <t>河北强盛风电设备有限公司</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -75856,28 +75856,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>841758.8199999999</v>
+        <v>849390.05</v>
       </c>
       <c r="D37" t="n">
-        <v>712595.34</v>
+        <v>3102047.68</v>
       </c>
       <c r="E37" t="n">
-        <v>951735.84</v>
+        <v>3102047.68</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>-5029903.22</v>
+        <v>-23906381.44</v>
       </c>
       <c r="H37" t="n">
-        <v>-1389903.22</v>
+        <v>-20266381.44</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>石家庄常宏智能科技有限公司</t>
+          <t>河北企合互帮科技发展有限公司</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -75886,28 +75886,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1298182.09</v>
+        <v>2526378.99</v>
       </c>
       <c r="D38" t="n">
-        <v>1656483.67</v>
+        <v>959198.3</v>
       </c>
       <c r="E38" t="n">
-        <v>1696350.79</v>
+        <v>318626.82</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>-12381736.48</v>
+        <v>-6123014.92</v>
       </c>
       <c r="H38" t="n">
-        <v>-8741736.48</v>
+        <v>-2483014.92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>河北强盛风电设备有限公司</t>
+          <t>衡橡科技股份有限公司</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -75916,28 +75916,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>849390.05</v>
+        <v>6412592.4</v>
       </c>
       <c r="D39" t="n">
-        <v>3102047.68</v>
+        <v>2046810.26</v>
       </c>
       <c r="E39" t="n">
-        <v>3102047.68</v>
+        <v>2040232.51</v>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>-23906381.44</v>
+        <v>-15457904.33</v>
       </c>
       <c r="H39" t="n">
-        <v>-20266381.44</v>
+        <v>-11817904.33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>河北锅圈食汇商业管理有限公司</t>
+          <t>石家庄市永通企业管理咨询有限公司</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -75946,28 +75946,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1210852.28</v>
+        <v>2832671.65</v>
       </c>
       <c r="D40" t="n">
-        <v>948137.02</v>
+        <v>3154117.27</v>
       </c>
       <c r="E40" t="n">
-        <v>1451991.47</v>
+        <v>5311017.58</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>-7178950.609999999</v>
+        <v>-26479838.47</v>
       </c>
       <c r="H40" t="n">
-        <v>-3538950.61</v>
+        <v>-22839838.47</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>河北联同医疗器械销售有限公司</t>
+          <t>欣诚信息技术有限公司</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -75976,28 +75976,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>636792.59</v>
+        <v>961524.5600000001</v>
       </c>
       <c r="D41" t="n">
-        <v>498641.77</v>
+        <v>940139.49</v>
       </c>
       <c r="E41" t="n">
-        <v>221726.06</v>
+        <v>186877.13</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>-2802218.45</v>
+        <v>-5857853.56</v>
       </c>
       <c r="H41" t="n">
-        <v>837781.55</v>
+        <v>-2217853.56</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>河北企合互帮科技发展有限公司</t>
+          <t>河北锅圈食汇商业管理有限公司</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -76006,178 +76006,178 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2526378.99</v>
+        <v>1210852.28</v>
       </c>
       <c r="D42" t="n">
-        <v>959198.3</v>
+        <v>948137.02</v>
       </c>
       <c r="E42" t="n">
-        <v>318626.82</v>
+        <v>1451991.47</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>-6123014.92</v>
+        <v>-7178950.609999999</v>
       </c>
       <c r="H42" t="n">
-        <v>-2483014.92</v>
+        <v>-3538950.61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>石家庄宽迈信息科技有限公司</t>
+          <t>石家庄氐宿企业管理咨询有限公司桥西分公司</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>663106.62</v>
+        <v>307170.35</v>
       </c>
       <c r="D43" t="n">
-        <v>437740.83</v>
+        <v>471163.98</v>
       </c>
       <c r="E43" t="n">
-        <v>356727.7</v>
+        <v>287874.26</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>-2510913.51</v>
+        <v>-2676022.12</v>
       </c>
       <c r="H43" t="n">
-        <v>1129086.49</v>
+        <v>963977.8800000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>兄弟团国际安保服务有限公司</t>
+          <t>河北永明地质工程机械有限公司</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>828229.5699999999</v>
+        <v>8852835.34</v>
       </c>
       <c r="D44" t="n">
-        <v>950458.85</v>
+        <v>1682278.66</v>
       </c>
       <c r="E44" t="n">
-        <v>2295.29</v>
+        <v>120986.15</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>-5745507.24</v>
+        <v>-10986936.77</v>
       </c>
       <c r="H44" t="n">
-        <v>-2105507.24</v>
+        <v>-7346936.77</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>河北宁强钢构集团有限公司</t>
+          <t>精晶药业股份有限公司</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2047133.94</v>
+        <v>2149793.84</v>
       </c>
       <c r="D45" t="n">
-        <v>6513697.08</v>
+        <v>2001662.49</v>
       </c>
       <c r="E45" t="n">
-        <v>8045945.26</v>
+        <v>2742971.55</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>-52731824.82</v>
+        <v>-15844608.98</v>
       </c>
       <c r="H45" t="n">
-        <v>-49091824.82</v>
+        <v>-12204608.98</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>劲超电线电缆有限公司</t>
+          <t>河北联同医疗器械销售有限公司</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>135807.16</v>
+        <v>636792.59</v>
       </c>
       <c r="D46" t="n">
-        <v>502962.86</v>
+        <v>498641.77</v>
       </c>
       <c r="E46" t="n">
-        <v>502962.86</v>
+        <v>221726.06</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>-3113702.879999999</v>
+        <v>-2802218.45</v>
       </c>
       <c r="H46" t="n">
-        <v>526297.1200000005</v>
+        <v>837781.55</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>河北维力斯羊绒纺织有限公司</t>
+          <t>际华三五零二职业装有限公司</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>682969.95</v>
+        <v>12754721.59</v>
       </c>
       <c r="D47" t="n">
-        <v>2615043.63</v>
+        <v>34899562.41</v>
       </c>
       <c r="E47" t="n">
-        <v>9823562.33</v>
+        <v>16120738.61</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>-27218867.74</v>
+        <v>-259507675.48</v>
       </c>
       <c r="H47" t="n">
-        <v>-23578867.74</v>
+        <v>-255867675.48</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司</t>
+          <t>河北宁强钢构集团有限公司</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -76186,28 +76186,28 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>65677123.44</v>
+        <v>2047133.94</v>
       </c>
       <c r="D48" t="n">
-        <v>156283177.79</v>
+        <v>6513697.08</v>
       </c>
       <c r="E48" t="n">
-        <v>133884169.3</v>
+        <v>8045945.26</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>-1226956413.83</v>
+        <v>-52731824.82</v>
       </c>
       <c r="H48" t="n">
-        <v>-1223316413.83</v>
+        <v>-49091824.82</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>石家庄沃尔森贸易有限公司</t>
+          <t>河北欣康投资有限公司</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -76216,28 +76216,28 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1869822.45</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>1491073.29</v>
+        <v>544409.64</v>
       </c>
       <c r="E49" t="n">
-        <v>873814.1</v>
+        <v>834352.49</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>-10401327.13</v>
+        <v>-3735219.970000001</v>
       </c>
       <c r="H49" t="n">
-        <v>-6761327.129999999</v>
+        <v>-95219.97000000044</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>石家庄市海森化工有限公司</t>
+          <t>兄弟团国际安保服务有限公司</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -76246,28 +76246,28 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>285308.42</v>
+        <v>828229.5699999999</v>
       </c>
       <c r="D50" t="n">
-        <v>408456.58</v>
+        <v>950458.85</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>2295.29</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>-1949196.06</v>
+        <v>-5745507.24</v>
       </c>
       <c r="H50" t="n">
-        <v>1690803.94</v>
+        <v>-2105507.24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>海南北纬十八度科技有限公司</t>
+          <t>河北维力斯羊绒纺织有限公司</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -76276,28 +76276,28 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1369732.99</v>
+        <v>682969.95</v>
       </c>
       <c r="D51" t="n">
-        <v>461043.4</v>
+        <v>2615043.63</v>
       </c>
       <c r="E51" t="n">
-        <v>451509.3</v>
+        <v>9823562.33</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>-2768813.1</v>
+        <v>-27218867.74</v>
       </c>
       <c r="H51" t="n">
-        <v>871186.8999999999</v>
+        <v>-23578867.74</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>河北欣康投资有限公司</t>
+          <t>石家庄沃尔森贸易有限公司</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -76306,28 +76306,28 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1869822.45</v>
       </c>
       <c r="D52" t="n">
-        <v>544409.64</v>
+        <v>1491073.29</v>
       </c>
       <c r="E52" t="n">
-        <v>834352.49</v>
+        <v>873814.1</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>-3735219.970000001</v>
+        <v>-10401327.13</v>
       </c>
       <c r="H52" t="n">
-        <v>-95219.97000000044</v>
+        <v>-6761327.129999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>河北绿诺食品有限公司</t>
+          <t>石家庄市海森化工有限公司</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -76336,28 +76336,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>163268.24</v>
+        <v>285308.42</v>
       </c>
       <c r="D53" t="n">
-        <v>1123362.75</v>
+        <v>408456.58</v>
       </c>
       <c r="E53" t="n">
-        <v>257265.7</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>-7210804.95</v>
+        <v>-1949196.06</v>
       </c>
       <c r="H53" t="n">
-        <v>-3570804.95</v>
+        <v>1690803.94</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>解放时代（吉林）新能源科技有限公司</t>
+          <t>石家庄彦发金属材料销售有限公司</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -76366,28 +76366,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>9592321.73</v>
+        <v>555794.46</v>
       </c>
       <c r="D54" t="n">
-        <v>8139516.01</v>
+        <v>985023.91</v>
       </c>
       <c r="E54" t="n">
-        <v>13229538.48</v>
+        <v>1143558.92</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>-69296150.55</v>
+        <v>-7128726.29</v>
       </c>
       <c r="H54" t="n">
-        <v>-65656150.55</v>
+        <v>-3488726.29</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>河北永旭电源有限公司</t>
+          <t>解放时代新能源科技有限公司</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -76396,28 +76396,28 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>26962775.03</v>
+        <v>65677123.44</v>
       </c>
       <c r="D55" t="n">
-        <v>1865462.96</v>
+        <v>156283177.79</v>
       </c>
       <c r="E55" t="n">
-        <v>26515.24</v>
+        <v>133884169.3</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>-12174755.96</v>
+        <v>-1226956413.83</v>
       </c>
       <c r="H55" t="n">
-        <v>-8534755.960000001</v>
+        <v>-1223316413.83</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>河北亚诚科技有限公司</t>
+          <t>河北永旭电源有限公司</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -76426,28 +76426,28 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2893146.15</v>
+        <v>26962775.03</v>
       </c>
       <c r="D56" t="n">
-        <v>2661664.94</v>
+        <v>1865462.96</v>
       </c>
       <c r="E56" t="n">
-        <v>2616835.33</v>
+        <v>26515.24</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>-20338489.91</v>
+        <v>-12174755.96</v>
       </c>
       <c r="H56" t="n">
-        <v>-16698489.91</v>
+        <v>-8534755.960000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>石家庄彦发金属材料销售有限公司</t>
+          <t>海南北纬十八度科技有限公司</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -76456,202 +76456,202 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>555794.46</v>
+        <v>1369732.99</v>
       </c>
       <c r="D57" t="n">
-        <v>985023.91</v>
+        <v>461043.4</v>
       </c>
       <c r="E57" t="n">
-        <v>1143558.92</v>
+        <v>451509.3</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>-7128726.29</v>
+        <v>-2768813.1</v>
       </c>
       <c r="H57" t="n">
-        <v>-3488726.29</v>
+        <v>871186.8999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>河北冀石云建设工程有限公司</t>
+          <t>河北亚诚科技有限公司</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>邸平花</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>472015.75</v>
+        <v>2893146.15</v>
       </c>
       <c r="D58" t="n">
-        <v>443320.09</v>
+        <v>2661664.94</v>
       </c>
       <c r="E58" t="n">
-        <v>578658.03</v>
+        <v>2616835.33</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>-2771898.66</v>
+        <v>-20338489.91</v>
       </c>
       <c r="H58" t="n">
-        <v>868101.3399999999</v>
+        <v>-16698489.91</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>河北文通国际贸易有限公司</t>
+          <t>解放时代（吉林）新能源科技有限公司</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5172907.01</v>
+        <v>9592321.73</v>
       </c>
       <c r="D59" t="n">
-        <v>5190279.6</v>
+        <v>8139516.01</v>
       </c>
       <c r="E59" t="n">
-        <v>5190279.6</v>
+        <v>13229538.48</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>-40612236.8</v>
+        <v>-69296150.55</v>
       </c>
       <c r="H59" t="n">
-        <v>-36972236.8</v>
+        <v>-65656150.55</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>河北文轩贸易有限公司</t>
+          <t>石家庄宽迈信息科技有限公司</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>620898.98</v>
+        <v>663106.62</v>
       </c>
       <c r="D60" t="n">
-        <v>4282108.85</v>
+        <v>437740.83</v>
       </c>
       <c r="E60" t="n">
-        <v>93739.86</v>
+        <v>356727.7</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>-29158501.81</v>
+        <v>-2510913.51</v>
       </c>
       <c r="H60" t="n">
-        <v>-25518501.81</v>
+        <v>1129086.49</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>河北益安诚人力资源服务有限公司</t>
+          <t>河北绿诺食品有限公司</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2387702.52</v>
+        <v>163268.24</v>
       </c>
       <c r="D61" t="n">
-        <v>2380909.83</v>
+        <v>1123362.75</v>
       </c>
       <c r="E61" t="n">
-        <v>2263042.01</v>
+        <v>257265.7</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>-18019410.82</v>
+        <v>-7210804.95</v>
       </c>
       <c r="H61" t="n">
-        <v>-14379410.82</v>
+        <v>-3570804.95</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>石家庄铭派机电有限公司</t>
+          <t>劲超电线电缆有限公司</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>855166.83</v>
+        <v>135807.16</v>
       </c>
       <c r="D62" t="n">
-        <v>1055659.03</v>
+        <v>502962.86</v>
       </c>
       <c r="E62" t="n">
-        <v>1326606.98</v>
+        <v>502962.86</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>-7806220.190000001</v>
+        <v>-3113702.879999999</v>
       </c>
       <c r="H62" t="n">
-        <v>-4166220.190000001</v>
+        <v>526297.1200000005</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>合一智慧物流服务（河北）有限公司</t>
+          <t>河北冀石云建设工程有限公司</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>邸平花</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>103827.62</v>
+        <v>472015.75</v>
       </c>
       <c r="D63" t="n">
-        <v>884737.75</v>
+        <v>443320.09</v>
       </c>
       <c r="E63" t="n">
-        <v>1959463.61</v>
+        <v>578658.03</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>-7242627.86</v>
+        <v>-2771898.66</v>
       </c>
       <c r="H63" t="n">
-        <v>-3602627.86</v>
+        <v>868101.3399999999</v>
       </c>
     </row>
   </sheetData>
